--- a/docs/xlsx/jobs-2026-09-21.xlsx
+++ b/docs/xlsx/jobs-2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="655">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1954 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Alaska Campaign Associate</t>
+  </si>
+  <si>
+    <t>Environment America</t>
+  </si>
+  <si>
+    <t>Anchorage, AK</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-alaska-campaign-associate-anchorage-alaska/6224313781</t>
+  </si>
+  <si>
+    <t>Animal Care Internship</t>
+  </si>
+  <si>
+    <t>Black Beauty Ranch</t>
+  </si>
+  <si>
+    <t>Murchsion, TX</t>
+  </si>
+  <si>
+    <t>Paid Internship</t>
+  </si>
+  <si>
+    <t>$13.39 per hour</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-animal-care-internship-murchsion-texas/6164937364</t>
+  </si>
+  <si>
+    <t>Aquatic Land Manager, Property &amp; Acquisition Specialist</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Tacoma, WA</t>
+  </si>
+  <si>
+    <t>$67,704 - $91,104 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-aquatic-land-manager-property--acquisition-specialist-tacoma-washington/3936469619</t>
+  </si>
+  <si>
+    <t>Aquatics Division, Assistant Assets Manager</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$102,888 - $119,976 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-aquatics-division-assistant-assets-manager-olympia-washington/6597628710</t>
+  </si>
+  <si>
+    <t>Associate Program Director-California</t>
+  </si>
+  <si>
+    <t>Conservation Lands Foundation</t>
+  </si>
+  <si>
+    <t>Southern California, CA</t>
+  </si>
+  <si>
+    <t>$72,500 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-associate-program-director-california-southern-california-california/1821655555</t>
+  </si>
+  <si>
+    <t>Botany/Hydro/Recreation/Visitor Services/Archeologist</t>
+  </si>
+  <si>
+    <t>USDA Forest Service Inyo National Forest</t>
+  </si>
+  <si>
+    <t>Bishop, CA</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$19.52 - $24.18 per hour</t>
+  </si>
+  <si>
+    <t>botany-hydrology-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-botanyhydrorecreationvisitor-servicesarcheologist-bishop-california/4013367183</t>
+  </si>
+  <si>
+    <t>Burn Area Restoration Implementation Leader</t>
+  </si>
+  <si>
+    <t>Altar Valley Conservation Alliance/USFWS</t>
+  </si>
+  <si>
+    <t>Yuma, AZ</t>
+  </si>
+  <si>
+    <t>$24.18 per hour</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-burn-area-restoration-implementation-leader-yuma-arizona/9946858894</t>
+  </si>
+  <si>
+    <t>Burn Area Restoration Technician</t>
+  </si>
+  <si>
+    <t>$23.07 per hour</t>
+  </si>
+  <si>
+    <t>botany-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-burn-area-restoration-technician-yuma-arizona/1665235384</t>
+  </si>
+  <si>
+    <t>Campaign Associate</t>
+  </si>
+  <si>
+    <t>PIRG</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-waste-is-out-of-fashion-campaigner-portland-oregon/1144399013</t>
+  </si>
+  <si>
+    <t>Canvass Office Director</t>
+  </si>
+  <si>
+    <t>Fund for the Public Interest</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this position is $40,000-$53,750, depending on position and location.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-washington-dc/4688406735</t>
+  </si>
+  <si>
+    <t>Minneapolis, MN</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-minneapolis-minnesota/1154941738</t>
+  </si>
+  <si>
+    <t>Denver, CO</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-denver-colorado/2334169700</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-canvass-office-director-chicago-illinois/5026634815</t>
+  </si>
+  <si>
+    <t>Custodial Manager I</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife- Indian Lodge</t>
+  </si>
+  <si>
+    <t>Davis Mountains State Park, TX</t>
+  </si>
+  <si>
+    <t>$46,623 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-custodial-manager-i-davis-mountains-state-park-texas/3503815790</t>
+  </si>
+  <si>
+    <t>Custodian II</t>
+  </si>
+  <si>
+    <t>$17.88 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-custodian-ii-davis-mountains-state-park-texas/1860014463</t>
+  </si>
+  <si>
+    <t>Depave for Trees Coordinator</t>
+  </si>
+  <si>
+    <t>Confluence Environmental Center</t>
+  </si>
+  <si>
+    <t>AmeriCorps</t>
+  </si>
+  <si>
+    <t>$1,688 per month</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-depave-for-trees-coordinator-portland-oregon/4396633560</t>
+  </si>
+  <si>
+    <t>Director and UW Extension Specialist</t>
+  </si>
+  <si>
+    <t>University of Wisconsin - Stevens Point College of Natural Resources</t>
+  </si>
+  <si>
+    <t>Stevens Point, WI</t>
+  </si>
+  <si>
+    <t>$74,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-and-uw-extension-specialist-stevens-point-wisconsin/1991613699</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>Western Resilience Center</t>
+  </si>
+  <si>
+    <t>Steamboat Springs, CO</t>
+  </si>
+  <si>
+    <t>$95,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-development-steamboat-springs-colorado/8860429988</t>
+  </si>
+  <si>
+    <t>Director of State Programs</t>
+  </si>
+  <si>
+    <t>Madison, WI</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation range for someone with 4-8 years of relevant experience is $43,500-$60,000.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-of-state-programs-madison-wisconsin/5868108720</t>
+  </si>
+  <si>
+    <t>Director, Climate Adaptation</t>
+  </si>
+  <si>
+    <t>Defenders of Wildlife</t>
+  </si>
+  <si>
+    <t>$127,000 - $143,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-ecology-policy-and-law-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-climate-adaptation-washington-dc/5516698302</t>
+  </si>
+  <si>
+    <t>Director, Conservation Technology</t>
+  </si>
+  <si>
+    <t>$143,000 - $155,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-director-conservation-technology-washington-dc/7439618849</t>
+  </si>
+  <si>
+    <t>District Forester (Burney Forestry District)</t>
+  </si>
+  <si>
+    <t>Sierra Pacific Industries</t>
+  </si>
+  <si>
+    <t>Burney, CA</t>
+  </si>
+  <si>
+    <t>$65,000 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-district-forester-burney-forestry-district-burney-california/6120204936</t>
+  </si>
+  <si>
+    <t>Environmental Ed &amp; Outdoor Rec Instructor</t>
+  </si>
+  <si>
+    <t>NorthWoods Stewardship Center</t>
+  </si>
+  <si>
+    <t>East Charleston, VT</t>
+  </si>
+  <si>
+    <t>Living stipend of $20,400</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-ed--outdoor-rec-instructor-east-charleston-vermont/4573042198</t>
+  </si>
+  <si>
+    <t>Environmental Scientist-Inspector</t>
+  </si>
+  <si>
+    <t>Office of Energy Infrastructure Safety</t>
+  </si>
+  <si>
+    <t>Sacramento, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $9,321 per month</t>
+  </si>
+  <si>
+    <t>ecology-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-scientist-inspector-sacramento-california/5151193470</t>
+  </si>
+  <si>
+    <t>Faculty Member in Chemistry</t>
+  </si>
+  <si>
+    <t>College of the Atlantic</t>
+  </si>
+  <si>
+    <t>Bar Harbor, ME</t>
+  </si>
+  <si>
+    <t>Faculty / Postdoc</t>
+  </si>
+  <si>
+    <t>$75,000 - $105,000 per year</t>
+  </si>
+  <si>
+    <t>ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-faculty-member-in-chemistry-bar-harbor-maine/8332952026</t>
+  </si>
+  <si>
+    <t>Federal Campaigns Associate</t>
+  </si>
+  <si>
+    <t>The target annual compensation for this entry-level position is $40,000 in the first year.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-federal-campaigns-associate-washington-dc/8822653368</t>
+  </si>
+  <si>
+    <t>Fish Hatchery Specialist 2 (In-Training) - Goldendale Hatchery - Career Seasonal - 2026-07563</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Goldendale, WA</t>
+  </si>
+  <si>
+    <t>$3,653 - $5,376 per month</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hatchery-specialist-2-in-training---goldendale-hatchery---career-seasonal---2026-07563-goldendale-washington/8090523138</t>
+  </si>
+  <si>
+    <t>Fish Hauling Supervisor - Construction &amp; Maintenance Project Supervisor - Permanent - 2026-07495</t>
+  </si>
+  <si>
+    <t>Lacey, WA</t>
+  </si>
+  <si>
+    <t>$6,229 - $7,224 per month</t>
+  </si>
+  <si>
+    <t>fisheries-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hauling-supervisor---construction--maintenance-project-supervisor---permanent---2026-07495-lacey-washington/5640494424</t>
+  </si>
+  <si>
+    <t>Habitat Connectivity Biologist - Fish &amp; Wildlife Biologist 4 - Permanent - 2026-07506</t>
+  </si>
+  <si>
+    <t>$5,928 - $7,973 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-habitat-connectivity-biologist---fish--wildlife-biologist-4---permanent---2026-07506-olympia-washington/4298431658</t>
+  </si>
+  <si>
+    <t>Hatchery Manager - Tutka Bay Lagoon Hatchery</t>
+  </si>
+  <si>
+    <t>Cook Inlet Aquaculture Association</t>
+  </si>
+  <si>
+    <t>Homer, AK</t>
+  </si>
+  <si>
+    <t>$63,923 - $83,487 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hatchery-manager---tutka-bay-lagoon-hatchery-homer-alaska/8739456671</t>
+  </si>
+  <si>
+    <t>Instructional Aide (Horticulture)</t>
+  </si>
+  <si>
+    <t>Los Angeles Unified School District</t>
+  </si>
+  <si>
+    <t>San Fernando, CA</t>
+  </si>
+  <si>
+    <t>$26.87 - $31.30 per hour</t>
+  </si>
+  <si>
+    <t>botany-environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-instructional-aide-horticulture-san-fernando-california/8256771799</t>
+  </si>
+  <si>
+    <t>Lake Rx Program Manager</t>
+  </si>
+  <si>
+    <t>Lilly Center for Lakes &amp; Streams</t>
+  </si>
+  <si>
+    <t>Winona Lake, IN</t>
+  </si>
+  <si>
+    <t>$64,000 - $69,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-lake-rx-program-manager-winona-lake-indiana/7091762963</t>
+  </si>
+  <si>
+    <t>Maintenance Technician (NPS, Haleakala National Park (Kipahulu)</t>
+  </si>
+  <si>
+    <t>Great Basin Institute</t>
+  </si>
+  <si>
+    <t>Makawao, HI</t>
+  </si>
+  <si>
+    <t>$26.30/hr</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-maintenance-technicians-nps-haleakala-national-park-kipahulu-makawao-hawaii/9177706667</t>
+  </si>
+  <si>
+    <t>Natural Resources Partnerships and Outreach Coordinator</t>
+  </si>
+  <si>
+    <t>$69,348 - $93,288 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-partnerships-and-outreach-coordinator-olympia-washington/5498183770</t>
+  </si>
+  <si>
+    <t>Natural Resources Safety &amp; Training Coordinator</t>
+  </si>
+  <si>
+    <t>Conservation Corps North Bay</t>
+  </si>
+  <si>
+    <t>San Rafael, CA</t>
+  </si>
+  <si>
+    <t>$70,304 per year</t>
+  </si>
+  <si>
+    <t>forestry-outdoor-recreation-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-safety--training-coordinator-san-rafael-california/8294408304</t>
+  </si>
+  <si>
+    <t>Naturalist - Outdoor School</t>
+  </si>
+  <si>
+    <t>Conejo Valley Unified School District</t>
+  </si>
+  <si>
+    <t>Thousand Oaks, CA</t>
+  </si>
+  <si>
+    <t>$21.50 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-naturalist---outdoor-school-thousand-oaks-california/6926012915</t>
+  </si>
+  <si>
+    <t>PhD Position in Aquatic Ecology in Iceland</t>
+  </si>
+  <si>
+    <t>University of Wisconsin</t>
+  </si>
+  <si>
+    <t>Student</t>
+  </si>
+  <si>
+    <t>$35,000 - $45,000 per year</t>
+  </si>
+  <si>
+    <t>ecology-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-phd-position-in-aquatic-ecology-in-iceland-madison-wisconsin/7450073306</t>
+  </si>
+  <si>
+    <t>Policy Analyst &amp; Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Western Landowners Alliance</t>
+  </si>
+  <si>
+    <t>$60,000 - $75,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-policy-analyst--communications-coordinator-denver-colorado/2603399501</t>
+  </si>
+  <si>
+    <t>Postdoctoral Researcher in Gray Whale Ecology and Biology</t>
+  </si>
+  <si>
+    <t>University of California Santa Barbara</t>
+  </si>
+  <si>
+    <t>Santa Barbara, CA</t>
+  </si>
+  <si>
+    <t>$71,491 - $85,736 per year</t>
+  </si>
+  <si>
+    <t>ecology-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-postdoctoral-researcher-in-gray-whale-ecology-and-biology-santa-barbara-california/6822451899</t>
+  </si>
+  <si>
+    <t>Prairie Restoration Field Crew Internship</t>
+  </si>
+  <si>
+    <t>The Phoenix Conservancy</t>
+  </si>
+  <si>
+    <t>Spokane, WA</t>
+  </si>
+  <si>
+    <t>$2000 stipend</t>
+  </si>
+  <si>
+    <t>botany-restoration-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-prairie-restoration-field-crew-internship-spokane-washington/4513119736</t>
+  </si>
+  <si>
+    <t>Program and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Northwest Land Conservation Trust</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>$25 - $28 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-and-operations-coordinator-eugene-oregon/1108664081</t>
+  </si>
+  <si>
+    <t>Program Director</t>
+  </si>
+  <si>
+    <t>Osprey Wilds Environmental Learning Center</t>
+  </si>
+  <si>
+    <t>Sandstone, MN</t>
+  </si>
+  <si>
+    <t>$60,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-director-sandstone-minnesota/5407174819</t>
+  </si>
+  <si>
+    <t>Riparian Lands Seed Steward</t>
+  </si>
+  <si>
+    <t>$31,000 per year</t>
+  </si>
+  <si>
+    <t>botany-ecology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-riparian-lands-seed-steward-east-charleston-vermont/1579900206</t>
+  </si>
+  <si>
+    <t>Shareholder Advocate</t>
+  </si>
+  <si>
+    <t>Green Century</t>
+  </si>
+  <si>
+    <t>Boston, MA</t>
+  </si>
+  <si>
+    <t>The starting target annual compensation range for someone with 2-5 years of relevant professional experience is $41,750-$46,000 in their first year.</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-shareholder-advocate-boston-massachusetts/1621957265</t>
+  </si>
+  <si>
+    <t>Sr. Conservation Manager, Conservation Campaigns</t>
+  </si>
+  <si>
+    <t>The Wilderness Society</t>
+  </si>
+  <si>
+    <t>Remote, Remote</t>
+  </si>
+  <si>
+    <t>$92,000 - $108,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-sr-conservation-manager-conservation-campaigns-remote-remote/3260734457</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>Wilderness Workshop</t>
+  </si>
+  <si>
+    <t>Carbondale, CO</t>
+  </si>
+  <si>
+    <t>$93,500 - $110,000 per year</t>
+  </si>
+  <si>
+    <t>policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-staff-attorney-carbondale-colorado/2697170610</t>
+  </si>
+  <si>
+    <t>TPWD - Customer Service Representative I</t>
+  </si>
+  <si>
+    <t>Texas Parks and Wildlife</t>
+  </si>
+  <si>
+    <t>Monahans, TX</t>
+  </si>
+  <si>
+    <t>$3,427.76 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---customer-service-representative-i-monahans-texas/5481106045</t>
+  </si>
+  <si>
+    <t>TPWD - Maintenance Specialist III (Operations Ranger)</t>
+  </si>
+  <si>
+    <t>Hueco Tanks State Park, TX</t>
+  </si>
+  <si>
+    <t>$3,920.64 per month</t>
+  </si>
+  <si>
+    <t>general-stewardship-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---maintenance-specialist-iii-operations-ranger-hueco-tanks-state-park-texas/5857077964</t>
+  </si>
+  <si>
+    <t>TPWD - Maintenance Specialist IV (Operations Ranger)</t>
+  </si>
+  <si>
+    <t>Fort Davis, TX</t>
+  </si>
+  <si>
+    <t>$4,137.06 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---maintenance-specialist-iv-operations-ranger-fort-davis-texas/5172822634</t>
+  </si>
+  <si>
+    <t>TPWD - Park/Historic Site Superintendent II (Park Superintendent)</t>
+  </si>
+  <si>
+    <t>Bracketville, TX</t>
+  </si>
+  <si>
+    <t>$6,139.85 - $7,139.85 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-tpwd---parkhistoric-site-superintendent-ii-park-superintendent-bracketville-texas/6085323054</t>
+  </si>
+  <si>
+    <t>Urban Forestry Project Manager</t>
+  </si>
+  <si>
+    <t>Great River Greening</t>
+  </si>
+  <si>
+    <t>Saint Paul, MN</t>
+  </si>
+  <si>
+    <t>$55,000 - $62,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-urban-forestry-project-manager-saint-paul-minnesota/7174706955</t>
+  </si>
+  <si>
+    <t>USDA-ARS Investigations of Pollinator Fitness</t>
+  </si>
+  <si>
+    <t>U.S. Department of Agriculture (USDA)</t>
+  </si>
+  <si>
+    <t>Stipend $5,800.00 – $6,000.00 Monthly</t>
+  </si>
+  <si>
+    <t>ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-investigations-of-pollinator-fitness-madison-wisconsin/9399042382</t>
+  </si>
+  <si>
+    <t>USDA-ARS Postdoctoral Research Opportunity in Plant Pathology</t>
+  </si>
+  <si>
+    <t>Salinas, CA</t>
+  </si>
+  <si>
+    <t>Stipend $80,000.00 – $87,000.00 Yearly</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-usda-ars-postdoctoral-research-opportunity-in-plant-pathology-salinas-california/9304123585</t>
+  </si>
+  <si>
+    <t>Vice President of Development &amp; Communications</t>
+  </si>
+  <si>
+    <t>Camp Fire Minneosta</t>
+  </si>
+  <si>
+    <t>Excelsior, MN</t>
+  </si>
+  <si>
+    <t>$115,000 - $125,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-of-development--communications-excelsior-minnesota/2375099674</t>
+  </si>
+  <si>
+    <t>Vice President, Philanthropy</t>
+  </si>
+  <si>
+    <t>Nature Conservancy of Canada</t>
+  </si>
+  <si>
+    <t>Toronto, Canada</t>
+  </si>
+  <si>
+    <t>$225,000 - $275,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-vice-president-philanthropy-toronto-canada/4346574428</t>
+  </si>
+  <si>
+    <t>Wildlife Husbandry Internship (Various positions)</t>
+  </si>
+  <si>
+    <t>White Oak Conservation</t>
+  </si>
+  <si>
+    <t>Yulee, FL</t>
+  </si>
+  <si>
+    <t>$2,400 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-husbandry-internship-various-positions-yulee-florida/1031381785</t>
+  </si>
+  <si>
+    <t>Working Lands Conservation Coordinator (California)</t>
+  </si>
+  <si>
+    <t>Monarch Joint Venture</t>
+  </si>
+  <si>
+    <t>Remote, CA</t>
+  </si>
+  <si>
+    <t>$26.44 - $33.65 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-working-lands-conservation-coordinator-california-remote-california/2886489156</t>
+  </si>
+  <si>
+    <t>3rd Grade Assistant Teacher</t>
+  </si>
+  <si>
+    <t>Two Rivers Public Charter School</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50919.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f69b36cc47b545a08e8a2ba12a9347cc-3rd-grade-assistant-teacher-two-rivers-public-charter-school-washington</t>
+  </si>
+  <si>
+    <t>Account Manager, Direct Mail</t>
+  </si>
+  <si>
+    <t>MissionWired</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 79001.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/1ee504c7aeba4bcd8d38de3940afe9cf-account-manager-direct-mail-missionwired-washington</t>
+  </si>
+  <si>
+    <t>Administrative Assistant - Autumn, Winter, &amp; Spring Saturday Academy (Part-time)</t>
+  </si>
+  <si>
+    <t>The Oliver Scholars Program Inc.</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 19.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4f3d954ce1fe41b5a6573dff203d58d7-administrative-assistant-autumn-winter-spring-saturday-academy-part-time-the-oliver-scholars-program-inc-new-york</t>
+  </si>
+  <si>
+    <t>Administrative Assistant (Temporary, 50%FTE)</t>
+  </si>
+  <si>
+    <t>Central California Environmental Justice Network</t>
+  </si>
+  <si>
+    <t>Fresno, California</t>
+  </si>
+  <si>
+    <t>USD 24.32 - 24.32/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Environment, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6a6ed695942244809211767a9f85ba96-administrative-assistant-temporary-50fte-central-california-environmental-justice-network-fresno</t>
+  </si>
+  <si>
+    <t>Advancement Director, Mid-Atlantic</t>
+  </si>
+  <si>
+    <t>Parkinson's Foundation</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/523884dc278a480c8e60fbbec4503108-advancement-director-mid-atlantic-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>After School Group Leader (Multiple Openings)</t>
+  </si>
+  <si>
+    <t>The YWCA of the City of New York</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 20.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Education, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6ef37cd384b243a991b29d71aeeb58ab-after-school-group-leader-multiple-openings-the-ywca-of-the-city-of-new-york-new-york</t>
+  </si>
+  <si>
+    <t>Attorney</t>
+  </si>
+  <si>
+    <t>Prisoners' Legal Services</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/87f439fe7a1b4217887e9da9b6042f24-attorney-prisoners-legal-services-boston</t>
+  </si>
+  <si>
+    <t>Bilingual Front Desk Receptionist (English/Spanish)</t>
+  </si>
+  <si>
+    <t>The Immigrant Law Center of Minnesota</t>
+  </si>
+  <si>
+    <t>USD 22.81/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1380cec91a9d44068f9f151998cf0e61-bilingual-front-desk-receptionist-englishspanish-the-immigrant-law-center-of-minnesota-saint-paul</t>
+  </si>
+  <si>
+    <t>Canvasser</t>
+  </si>
+  <si>
+    <t>Make the Road Action</t>
+  </si>
+  <si>
+    <t>Winnemucca, Nevada</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a31ea881b7da422aa80e8a5dfefedf87-canvasser-make-the-road-action-winnemucca</t>
+  </si>
+  <si>
+    <t>Reno, Nevada</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f1efe4ccbdbf4f8d9c2e34be6d9276fd-canvasser-make-the-road-action-reno</t>
+  </si>
+  <si>
+    <t>Canvasser Lead</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e2b5164bb487457fbe0a8cfc93c54b78-canvasser-lead-make-the-road-action-winnemucca</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d62a73b5801147679992d44cc4756b0e-canvasser-lead-make-the-road-action-reno</t>
+  </si>
+  <si>
+    <t>Career Development Specialist</t>
+  </si>
+  <si>
+    <t>Urban Pathways</t>
+  </si>
+  <si>
+    <t>USD 49863.51 - 67315.74/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/efa7d4fd50004e719d445f780d6134c5-career-development-specialist-urban-pathways-new-york</t>
+  </si>
+  <si>
+    <t>Chofer</t>
+  </si>
+  <si>
+    <t>Médicos del Mundo Suiza, Misión México</t>
+  </si>
+  <si>
+    <t>Ciudad de México, Ciudad de México, MX</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>MXN 13000.00 - 13000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Reproductive Health Rights</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ed01cebfe4e947eb91d54de61ce38f0a-chofer-medicos-del-mundo-suiza-mision-mexico-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Communications &amp; Social Media Coordinator</t>
+  </si>
+  <si>
+    <t>30Rights</t>
+  </si>
+  <si>
+    <t>Remote (Texas)</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8a879c4366fd4ae9afce68c6f38f6547-communications-social-media-coordinator-30rights-fort-worth</t>
+  </si>
+  <si>
+    <t>Community Engagement &amp; Development Manager</t>
+  </si>
+  <si>
+    <t>Baltimore SquashWise</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Sports Recreation, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cd9fc9af7a804f34b11f32d5779ed162-community-engagement-development-manager-baltimore-squashwise-baltimore</t>
+  </si>
+  <si>
+    <t>Community Operations Coordinator</t>
+  </si>
+  <si>
+    <t>United South End Settlements</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ee4624dc9cb34f65993a5e7c8f488e40-community-operations-coordinator-united-south-end-settlements-boston</t>
+  </si>
+  <si>
+    <t>COMMUNITY ORGANIZER</t>
+  </si>
+  <si>
+    <t>Los Angeles Alliance for a New Economy</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>USD 73000.00 - 76000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Job Workplace, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fbf5139865af4bbd97cb370ddce4b214-community-organizer-los-angeles-alliance-for-a-new-economy-los-angeles</t>
+  </si>
+  <si>
+    <t>Contract Writing Editor</t>
+  </si>
+  <si>
+    <t>EdReports</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>USD 100.00/hour</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cfb15f659f20403892322c25f120ae72-contract-writing-editor-edreports-raleigh</t>
+  </si>
+  <si>
+    <t>Coordinador/a Territorial Programa de Fortalecimiento y Desarrollo de Cadenas Productivas - TARTAGAL</t>
+  </si>
+  <si>
+    <t>Asociación Civil Pata Pila</t>
+  </si>
+  <si>
+    <t>Tartagal, Salta, AR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6559d98682c3412c941e2ae7e1850dbe-coordinadora-territorial-programa-de-fortalecimiento-y-desarrollo-de-cadenas-productivas-tartagal-asociacion-civil-pata-pila-tartagal</t>
+  </si>
+  <si>
+    <t>Coordinateur HR - Central African Republic</t>
+  </si>
+  <si>
+    <t>INTERSOS</t>
+  </si>
+  <si>
+    <t>Bangui, Bangui, CF</t>
+  </si>
+  <si>
+    <t>EUR 3690.00 - 4245.00/month</t>
+  </si>
+  <si>
+    <t>International Relations, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/157736c2a2f64dc6bf560ef413c2e660-coordinateur-hr-central-african-republic-intersos-bangui</t>
+  </si>
+  <si>
+    <t>Coordinator, Total Rewards</t>
+  </si>
+  <si>
+    <t>National Geographic Society</t>
+  </si>
+  <si>
+    <t>Remote (Washington, DC)</t>
+  </si>
+  <si>
+    <t>USD 27.41 - 28.85/hour</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/aa5e5d2c8aad4d198651587eaf5ea402-coordinator-total-rewards-national-geographic-society-washington</t>
+  </si>
+  <si>
+    <t>Database and Development Coordinator</t>
+  </si>
+  <si>
+    <t>Ecumenical Ministries of Oregon</t>
+  </si>
+  <si>
+    <t>Portland, Oregon</t>
+  </si>
+  <si>
+    <t>USD 31.19/hour</t>
+  </si>
+  <si>
+    <t>Environment, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/78caed167db94989834d48f8c82e7364-database-and-development-coordinator-ecumenical-ministries-of-oregon-portland</t>
+  </si>
+  <si>
+    <t>Development Manager, New York Chapter</t>
+  </si>
+  <si>
+    <t>Remote (Rochester, New York)</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4411f20ae1a0459f907352cf74d35082-development-manager-new-york-chapter-parkinsons-foundation-rochester</t>
+  </si>
+  <si>
+    <t>Director (a) de Conservación e Investigación</t>
+  </si>
+  <si>
+    <t>Conservacion del oso de anteojos - SBC</t>
+  </si>
+  <si>
+    <t>Urubamba, Cuzco, PE</t>
+  </si>
+  <si>
+    <t>PEN 7000.00 - 10000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b875a447b871457d8dddc1d455e88b00-director-a-de-conservacion-e-investigacion-conservacion-del-oso-de-anteojos-sbc-urubamba</t>
+  </si>
+  <si>
+    <t>The Redford Center</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Media</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ec13cb1968a4566a23cfceeacff3511-director-of-development-the-redford-center-san-francisco</t>
+  </si>
+  <si>
+    <t>Director of Operations - Idaho BaseCamp</t>
+  </si>
+  <si>
+    <t>Idaho Base Camp - IBC</t>
+  </si>
+  <si>
+    <t>Hailey, Idaho</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bcabff4e082647f8a659615c4d769dc9-director-of-operations-idaho-basecamp-idaho-base-camp-ibc-hailey</t>
+  </si>
+  <si>
+    <t>Director of Social Services</t>
+  </si>
+  <si>
+    <t>USD 66453.61 - 89712.38/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d7c77afbfbe14afeb1e2730963fd4f86-director-of-social-services-urban-pathways-new-york</t>
+  </si>
+  <si>
+    <t>Director, Global Food Sovereignty Movements Program</t>
+  </si>
+  <si>
+    <t>WhyHunger</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Human Rights Civil Liberties, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f7d755cc501c48bdaf62ed4f8c5320e4-director-global-food-sovereignty-movements-program-whyhunger-remote</t>
+  </si>
+  <si>
+    <t>Director, Strategic Relationships</t>
+  </si>
+  <si>
+    <t>Heifer International</t>
+  </si>
+  <si>
+    <t>USD 145000.00 - 165000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Poverty, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61121d985e4c4429b9b280ca6c9c96d7-director-strategic-relationships-heifer-international-little-rock</t>
+  </si>
+  <si>
+    <t>Education Program Specialist</t>
+  </si>
+  <si>
+    <t>Treatment Advocacy Center</t>
+  </si>
+  <si>
+    <t>USD 68000.00 - 72000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Mental Health, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6c8247a0f969472c85ca980693ca64c4-education-program-specialist-treatment-advocacy-center-alexandria</t>
+  </si>
+  <si>
+    <t>ELEMENTARY PROGRAM FACILITATOR</t>
+  </si>
+  <si>
+    <t>Girls Inc of the Island City</t>
+  </si>
+  <si>
+    <t>Alameda, California</t>
+  </si>
+  <si>
+    <t>USD 26.40 - 26.40/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a7a77fd230c3437a9870d88008b1ec97-elementary-program-facilitator-girls-inc-of-the-island-city-alameda</t>
+  </si>
+  <si>
+    <t>Especialista de Língua Portuguesa</t>
+  </si>
+  <si>
+    <t>FUNDAÇÃO GENIANTIS</t>
+  </si>
+  <si>
+    <t>São Paulo, São Paulo, BR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/970dd34cd2c644b486597b04e436f54a-especialista-de-lingua-portuguesa-fundacao-geniantis-sao-paulo</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Sacred Threads</t>
+  </si>
+  <si>
+    <t>Newton, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f846957a398d47fdb242875b8fe6e24b-executive-director-sacred-threads-newton</t>
+  </si>
+  <si>
+    <t>Family Defense Unit Social Worker - White Plains</t>
+  </si>
+  <si>
+    <t>Legal Services of the Hudson Valley</t>
+  </si>
+  <si>
+    <t>White Plains, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24ed164eeb8e4ecd91b5aac43413dc1e-family-defense-unit-social-worker-white-plains-legal-services-of-the-hudson-valley-white-plains</t>
+  </si>
+  <si>
+    <t>Finance Specialist</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b124544b440940b98bcb7916d44ca0fa-finance-specialist-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Fractional Communications &amp; Digital Content Coordinator</t>
+  </si>
+  <si>
+    <t>WellBeing International, Inc.</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 60.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Community Development, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9ad24e8f9d1046a3b871f800c8d78ce1-fractional-communications-digital-content-coordinator-wellbeing-international-inc-chevy-chase</t>
+  </si>
+  <si>
+    <t>Gerente/a de Captación y Recaudación de Fondos.</t>
+  </si>
+  <si>
+    <t>World Vision México</t>
+  </si>
+  <si>
+    <t>MXN 50000.00 - 55000.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cc92143d97ee4906870018bd2057ebbf-gerentea-de-captacion-y-recaudacion-de-fondos-world-vision-mexico-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>HR Talent Aquisition Associate</t>
+  </si>
+  <si>
+    <t>Rising Ground</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8557e778c72a4975a4f52efbda9947ae-hr-talent-aquisition-associate-rising-ground-new-york</t>
+  </si>
+  <si>
+    <t>Human Resources Coordinator -National</t>
+  </si>
+  <si>
+    <t>The Posse Foundation, Inc.</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dee0c5789007466d84e4a33821f0498e-human-resources-coordinator-national-the-posse-foundation-inc-new-york</t>
+  </si>
+  <si>
+    <t>Hunter Health Intake Support Specialist</t>
+  </si>
+  <si>
+    <t>Project Alive</t>
+  </si>
+  <si>
+    <t>USD 28.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6372ac70ddf4804aad64da97db94bc5-hunter-health-intake-support-specialist-project-alive-davenport</t>
+  </si>
+  <si>
+    <t>Immigration Bond Fund Coordinator</t>
+  </si>
+  <si>
+    <t>Orange County Justice Fund</t>
+  </si>
+  <si>
+    <t>Santa Ana, California</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a894dd57f154564bed9d74f18981519-immigration-bond-fund-coordinator-orange-county-justice-fund-santa-ana</t>
+  </si>
+  <si>
+    <t>Impact Analyst, Equitable Learning &amp; Measurement</t>
+  </si>
+  <si>
+    <t>TBF -The Boston Foundation</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3a3f87cd88ed46ac85abaaa7701a7ce7-impact-analyst-equitable-learning-measurement-tbf-the-boston-foundation-boston</t>
+  </si>
+  <si>
+    <t>Internal Communications Lead</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 87000.00 - 97000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f58d2715a84446caced115f430e396e-internal-communications-lead-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>International Director</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>USD 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b09f43dc456c4d0fa24f7fb1e86075d6-international-director-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Lead Street Outreach Case Manager</t>
+  </si>
+  <si>
+    <t>Everyone Home DC</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/da98bbda55004378b72796dc36ec60b2-lead-street-outreach-case-manager-everyone-home-dc-washington</t>
+  </si>
+  <si>
+    <t>LEDA Special Events &amp; Advancement Operations Officer</t>
+  </si>
+  <si>
+    <t>(LEDA) Leadership Enterprise for a Diverse America</t>
+  </si>
+  <si>
+    <t>USD 56000.00 - 56000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/911d6003ad3843f8b1c43d5050a77669-leda-special-events-advancement-operations-officer-leda-leadership-enterprise-for-a-diverse-america-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Development</t>
+  </si>
+  <si>
+    <t>Future Caucus</t>
+  </si>
+  <si>
+    <t>USD 72750.00 - 76200.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/637a51a963e147f9a018d46c8f2473d3-manager-development-future-caucus-washington</t>
+  </si>
+  <si>
+    <t>Metro Detroit Program Facilitator</t>
+  </si>
+  <si>
+    <t>Beyond Bedtime (formerly Pajama Program)</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/17c1b2b4a5bb402e8f1843995293047c-metro-detroit-program-facilitator-beyond-bedtime-formerly-pajama-program-detroit</t>
+  </si>
+  <si>
+    <t>MSF busca Psiquiatra (Cd Mx)</t>
+  </si>
+  <si>
+    <t>Médicos Sin Fronteras en México AC</t>
+  </si>
+  <si>
+    <t>MXN 46888.00 - 46888.00/month</t>
+  </si>
+  <si>
+    <t>Health Medicine, Victim Support, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/57e740f972aa43038fbcf59fb3327c9e-msf-busca-psiquiatra-cd-mx-medicos-sin-fronteras-en-mexico-ac-ciudad-de-mexico</t>
+  </si>
+  <si>
+    <t>Partnerships Manager</t>
+  </si>
+  <si>
+    <t>826NYC</t>
+  </si>
+  <si>
+    <t>Kings County, New York</t>
+  </si>
+  <si>
+    <t>USD 53000.00 - 56500.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e74553ce98b048d8a37ae04a76789f68-partnerships-manager-826nyc-kings-county</t>
+  </si>
+  <si>
+    <t>People Operations Specialist</t>
+  </si>
+  <si>
+    <t>Partners for Sacred Places</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Civic Engagement, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c37fdaccec5d47f0b48d044b4e8d5835-people-operations-specialist-partners-for-sacred-places-philadelphia</t>
+  </si>
+  <si>
+    <t>Program Administration Coordinator</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e705dc94dd3146398d5e46d031d8479a-program-administration-coordinator-united-south-end-settlements-boston</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Coachella Valley</t>
+  </si>
+  <si>
+    <t>Armed Services Arts Partnership (ASAP)</t>
+  </si>
+  <si>
+    <t>Remote (Coachella, California)</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 55000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Veterans</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1289a58ae38943438cc6ec2d99ca13bb-program-coordinator-coachella-valley-armed-services-arts-partnership-asap-coachella</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Continuing Education</t>
+  </si>
+  <si>
+    <t>American Society of Clinical Oncology</t>
+  </si>
+  <si>
+    <t>Alexandria, VA</t>
+  </si>
+  <si>
+    <t>USD 29.79 - 39.18/hour</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a48836e3d93c4f148d50149409991384-program-coordinator-continuing-education-american-society-of-clinical-oncology-alexandria</t>
+  </si>
+  <si>
+    <t>Program Operations Associate, Conservation Innovation</t>
+  </si>
+  <si>
+    <t>Open Space Institute</t>
+  </si>
+  <si>
+    <t>USD 66000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/72fe8fd7cd954baab1c74bec14b84756-program-operations-associate-conservation-innovation-open-space-institute-new-york</t>
+  </si>
+  <si>
+    <t>Project Coordinator</t>
+  </si>
+  <si>
+    <t>Middle States Association Commissions on Elementary and Secondary Schools</t>
+  </si>
+  <si>
+    <t>USD 49000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/80bd98346d944eb59f9af1c115ff09ba-project-coordinator-middle-states-association-commissions-on-elementary-and-secondary-schools-philadelphia</t>
+  </si>
+  <si>
+    <t>Remote Grant Writer</t>
+  </si>
+  <si>
+    <t>The Bear Creek School</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b4ff428ac62e4e80aaa6edb56581b37a-remote-grant-writer-the-bear-creek-school-redmond</t>
+  </si>
+  <si>
+    <t>Salesforce Architect or Senior Architect</t>
+  </si>
+  <si>
+    <t>Coefficient Giving</t>
+  </si>
+  <si>
+    <t>USD 179975.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Health Medicine, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2f581923a1fe4c48b1dc674eefe0b501-salesforce-architect-or-senior-architect-coefficient-giving-san-francisco</t>
+  </si>
+  <si>
+    <t>Senior Associate (CityStart &amp; Emergency Financial Empowerment)</t>
+  </si>
+  <si>
+    <t>Cities for Financial Empowerment Fund</t>
+  </si>
+  <si>
+    <t>USD 72900.00 - 97500.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Economic Development, Financial Literacy Personal Finance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/878f094228044a4c98bfd42337a74f37-senior-associate-citystart-emergency-financial-empowerment-cities-for-financial-empowerment-fund-new-york</t>
+  </si>
+  <si>
+    <t>Senior Director, Data Operations</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a02907a55b5f46618e64f867716a0acc-senior-director-data-operations-parkinsons-foundation-miami</t>
+  </si>
+  <si>
+    <t>Senior Evaluation Associate</t>
+  </si>
+  <si>
+    <t>Hatch Creative Strategy</t>
+  </si>
+  <si>
+    <t>USD 72000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/d784913578ad4e7487a30ddad8398e47-senior-evaluation-associate-hatch-creative-strategy-new-orleans</t>
+  </si>
+  <si>
+    <t>Senior Grant Accountant - White Plains</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a6b82b9eaa8470e948eed00fcf9823e-senior-grant-accountant-white-plains-legal-services-of-the-hudson-valley-white-plains</t>
+  </si>
+  <si>
+    <t>Senior Manager, Homeownership Programs</t>
+  </si>
+  <si>
+    <t>Habitat for Humanity Chicago</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c732e730a1044ac6855a53c383ac63b6-senior-manager-homeownership-programs-habitat-for-humanity-chicago-chicago</t>
+  </si>
+  <si>
+    <t>Senior Salesforce Administrator and Business Analyst</t>
+  </si>
+  <si>
+    <t>USD 155825.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a285905d8a2544309d09424f5c3843c7-senior-salesforce-administrator-and-business-analyst-coefficient-giving-san-francisco</t>
+  </si>
+  <si>
+    <t>Social Enterprise &amp; Youth Development Manager</t>
+  </si>
+  <si>
+    <t>Allies In Caring, Inc.</t>
+  </si>
+  <si>
+    <t>Hammonton, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 78000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7094856a019940fc871c5efd5966b7ba-social-enterprise-youth-development-manager-allies-in-caring-inc-hammonton</t>
+  </si>
+  <si>
+    <t>Staff Accountant</t>
+  </si>
+  <si>
+    <t>The Choice Inc</t>
+  </si>
+  <si>
+    <t>Arlington, Virginia</t>
+  </si>
+  <si>
+    <t>USD 35.00 - 40.00/hour</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/005dd29475ae49e0b0176c1a0418460c-staff-accountant-the-choice-inc-arlington</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>USD 90262.00 - 100532.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d3921d88e6cf4be4871a2dc7b4334169-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
+    <t>Immigration Center for Women and Children</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>USD 78000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Immigrants Or Refugees, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/bc95ecc7ea574742be0fe0ee2409fd98-staff-attorney-immigration-center-for-women-and-children-los-angeles</t>
+  </si>
+  <si>
+    <t>Support Coordinator</t>
+  </si>
+  <si>
+    <t>Community Living Services</t>
+  </si>
+  <si>
+    <t>USD 50112.00 - 50112.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Family, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/ed5d264551574260aa573194a6f3ce0d-support-coordinator-community-living-services-detroit</t>
+  </si>
+  <si>
+    <t>Vice President, Government Relations &amp; Political Affairs</t>
+  </si>
+  <si>
+    <t>League of Conservation Voters</t>
+  </si>
+  <si>
+    <t>USD 147900.00 - 200940.00/year</t>
+  </si>
+  <si>
+    <t>Climate Change, Environment, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39d44c37065247d68023cf114a4ae45b-vice-president-government-relations-political-affairs-league-of-conservation-voters-washington</t>
+  </si>
+  <si>
+    <t>Workers' Rights Organizer - Temporary</t>
+  </si>
+  <si>
+    <t>TSNE</t>
+  </si>
+  <si>
+    <t>USD 30.00 - 33.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/db8380cb89db4983a5b2656a5dab9182-workers-rights-organizer-temporary-tsne-new-york</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1995,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +2021,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +2403,1378 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" t="s">
+        <v>93</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>99</v>
+      </c>
+      <c r="F20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" t="s">
+        <v>108</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>110</v>
+      </c>
+      <c r="B23" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" t="s">
+        <v>125</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>134</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>135</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>143</v>
+      </c>
+      <c r="B29" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>145</v>
+      </c>
+      <c r="F29" t="s">
+        <v>146</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>148</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" t="s">
+        <v>149</v>
+      </c>
+      <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>152</v>
+      </c>
+      <c r="B31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>155</v>
+      </c>
+      <c r="F31" t="s">
+        <v>141</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" t="s">
+        <v>160</v>
+      </c>
+      <c r="F32" t="s">
+        <v>161</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" t="s">
+        <v>95</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>168</v>
+      </c>
+      <c r="B34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>173</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" t="s">
+        <v>174</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>177</v>
+      </c>
+      <c r="B36" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" t="s">
+        <v>180</v>
+      </c>
+      <c r="F36" t="s">
+        <v>181</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B37" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" t="s">
+        <v>185</v>
+      </c>
+      <c r="D37" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" t="s">
+        <v>187</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>189</v>
+      </c>
+      <c r="B38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" t="s">
+        <v>98</v>
+      </c>
+      <c r="D38" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>195</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" t="s">
+        <v>201</v>
+      </c>
+      <c r="D40" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" t="s">
+        <v>203</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>205</v>
+      </c>
+      <c r="B41" t="s">
+        <v>206</v>
+      </c>
+      <c r="C41" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" t="s">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s">
+        <v>208</v>
+      </c>
+      <c r="F41" t="s">
+        <v>209</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" t="s">
+        <v>214</v>
+      </c>
+      <c r="F42" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>217</v>
+      </c>
+      <c r="B43" t="s">
+        <v>218</v>
+      </c>
+      <c r="C43" t="s">
+        <v>219</v>
+      </c>
+      <c r="D43" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" t="s">
+        <v>220</v>
+      </c>
+      <c r="F43" t="s">
+        <v>221</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>223</v>
+      </c>
+      <c r="B44" t="s">
+        <v>116</v>
+      </c>
+      <c r="C44" t="s">
+        <v>117</v>
+      </c>
+      <c r="D44" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" t="s">
+        <v>224</v>
+      </c>
+      <c r="F44" t="s">
+        <v>225</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>227</v>
+      </c>
+      <c r="B45" t="s">
+        <v>228</v>
+      </c>
+      <c r="C45" t="s">
+        <v>229</v>
+      </c>
+      <c r="D45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" t="s">
+        <v>230</v>
+      </c>
+      <c r="F45" t="s">
+        <v>13</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>232</v>
+      </c>
+      <c r="B46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C46" t="s">
+        <v>234</v>
+      </c>
+      <c r="D46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" t="s">
+        <v>235</v>
+      </c>
+      <c r="F46" t="s">
+        <v>13</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" t="s">
+        <v>240</v>
+      </c>
+      <c r="F47" t="s">
+        <v>241</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>243</v>
+      </c>
+      <c r="B48" t="s">
+        <v>244</v>
+      </c>
+      <c r="C48" t="s">
+        <v>245</v>
+      </c>
+      <c r="D48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" t="s">
+        <v>246</v>
+      </c>
+      <c r="F48" t="s">
+        <v>89</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>248</v>
+      </c>
+      <c r="B49" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" t="s">
+        <v>249</v>
+      </c>
+      <c r="D49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" t="s">
+        <v>250</v>
+      </c>
+      <c r="F49" t="s">
+        <v>251</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>253</v>
+      </c>
+      <c r="B50" t="s">
+        <v>244</v>
+      </c>
+      <c r="C50" t="s">
+        <v>254</v>
+      </c>
+      <c r="D50" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" t="s">
+        <v>255</v>
+      </c>
+      <c r="F50" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>257</v>
+      </c>
+      <c r="B51" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" t="s">
+        <v>258</v>
+      </c>
+      <c r="D51" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" t="s">
+        <v>259</v>
+      </c>
+      <c r="F51" t="s">
+        <v>251</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>261</v>
+      </c>
+      <c r="B52" t="s">
+        <v>262</v>
+      </c>
+      <c r="C52" t="s">
+        <v>263</v>
+      </c>
+      <c r="D52" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" t="s">
+        <v>264</v>
+      </c>
+      <c r="F52" t="s">
+        <v>265</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>267</v>
+      </c>
+      <c r="B53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" t="s">
+        <v>98</v>
+      </c>
+      <c r="D53" t="s">
+        <v>18</v>
+      </c>
+      <c r="E53" t="s">
+        <v>269</v>
+      </c>
+      <c r="F53" t="s">
+        <v>270</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>272</v>
+      </c>
+      <c r="B54" t="s">
+        <v>268</v>
+      </c>
+      <c r="C54" t="s">
+        <v>273</v>
+      </c>
+      <c r="D54" t="s">
+        <v>130</v>
+      </c>
+      <c r="E54" t="s">
+        <v>274</v>
+      </c>
+      <c r="F54" t="s">
+        <v>225</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>276</v>
+      </c>
+      <c r="B55" t="s">
+        <v>277</v>
+      </c>
+      <c r="C55" t="s">
+        <v>278</v>
+      </c>
+      <c r="D55" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" t="s">
+        <v>279</v>
+      </c>
+      <c r="F55" t="s">
+        <v>89</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>281</v>
+      </c>
+      <c r="B56" t="s">
+        <v>282</v>
+      </c>
+      <c r="C56" t="s">
+        <v>283</v>
+      </c>
+      <c r="D56" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" t="s">
+        <v>284</v>
+      </c>
+      <c r="F56" t="s">
+        <v>89</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>286</v>
+      </c>
+      <c r="B57" t="s">
+        <v>287</v>
+      </c>
+      <c r="C57" t="s">
+        <v>288</v>
+      </c>
+      <c r="D57" t="s">
+        <v>18</v>
+      </c>
+      <c r="E57" t="s">
+        <v>289</v>
+      </c>
+      <c r="F57" t="s">
+        <v>20</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>291</v>
+      </c>
+      <c r="B58" t="s">
+        <v>292</v>
+      </c>
+      <c r="C58" t="s">
+        <v>293</v>
+      </c>
+      <c r="D58" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" t="s">
+        <v>294</v>
+      </c>
+      <c r="F58" t="s">
+        <v>150</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +3830,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +3869,1738 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E4" t="s">
+        <v>313</v>
+      </c>
+      <c r="F4" t="s">
+        <v>301</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D5" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" t="s">
+        <v>318</v>
+      </c>
+      <c r="F5" t="s">
+        <v>319</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C6" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E6" t="s">
+        <v>323</v>
+      </c>
+      <c r="F6" t="s">
+        <v>324</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B7" t="s">
+        <v>327</v>
+      </c>
+      <c r="C7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E7" t="s">
+        <v>329</v>
+      </c>
+      <c r="F7" t="s">
+        <v>330</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C8" t="s">
+        <v>334</v>
+      </c>
+      <c r="D8" t="s">
+        <v>299</v>
+      </c>
+      <c r="E8" t="s">
+        <v>335</v>
+      </c>
+      <c r="F8" t="s">
+        <v>336</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>338</v>
+      </c>
+      <c r="B9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C9" t="s">
+        <v>263</v>
+      </c>
+      <c r="D9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" t="s">
+        <v>340</v>
+      </c>
+      <c r="F9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" t="s">
+        <v>344</v>
+      </c>
+      <c r="C10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" t="s">
+        <v>312</v>
+      </c>
+      <c r="E10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F10" t="s">
+        <v>347</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>343</v>
+      </c>
+      <c r="B11" t="s">
+        <v>344</v>
+      </c>
+      <c r="C11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D11" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F11" t="s">
+        <v>347</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>351</v>
+      </c>
+      <c r="B12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F12" t="s">
+        <v>347</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>351</v>
+      </c>
+      <c r="B13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C13" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F13" t="s">
+        <v>347</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>355</v>
+      </c>
+      <c r="B14" t="s">
+        <v>356</v>
+      </c>
+      <c r="C14" t="s">
+        <v>311</v>
+      </c>
+      <c r="D14" t="s">
+        <v>299</v>
+      </c>
+      <c r="E14" t="s">
+        <v>357</v>
+      </c>
+      <c r="F14" t="s">
+        <v>358</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>360</v>
+      </c>
+      <c r="B15" t="s">
+        <v>361</v>
+      </c>
+      <c r="C15" t="s">
+        <v>362</v>
+      </c>
+      <c r="D15" t="s">
+        <v>363</v>
+      </c>
+      <c r="E15" t="s">
+        <v>364</v>
+      </c>
+      <c r="F15" t="s">
+        <v>365</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>367</v>
+      </c>
+      <c r="B16" t="s">
+        <v>368</v>
+      </c>
+      <c r="C16" t="s">
+        <v>369</v>
+      </c>
+      <c r="D16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E16" t="s">
+        <v>370</v>
+      </c>
+      <c r="F16" t="s">
+        <v>371</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>373</v>
+      </c>
+      <c r="B17" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" t="s">
+        <v>299</v>
+      </c>
+      <c r="E17" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" t="s">
+        <v>377</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>379</v>
+      </c>
+      <c r="B18" t="s">
+        <v>380</v>
+      </c>
+      <c r="C18" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" t="s">
+        <v>299</v>
+      </c>
+      <c r="E18" t="s">
+        <v>381</v>
+      </c>
+      <c r="F18" t="s">
+        <v>382</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19" t="s">
+        <v>385</v>
+      </c>
+      <c r="C19" t="s">
+        <v>386</v>
+      </c>
+      <c r="D19" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" t="s">
+        <v>387</v>
+      </c>
+      <c r="F19" t="s">
+        <v>388</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>390</v>
+      </c>
+      <c r="B20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D20" t="s">
+        <v>392</v>
+      </c>
+      <c r="E20" t="s">
+        <v>393</v>
+      </c>
+      <c r="F20" t="s">
+        <v>394</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>396</v>
+      </c>
+      <c r="B21" t="s">
+        <v>397</v>
+      </c>
+      <c r="C21" t="s">
+        <v>398</v>
+      </c>
+      <c r="D21" t="s">
+        <v>299</v>
+      </c>
+      <c r="E21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F21" t="s">
+        <v>399</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>401</v>
+      </c>
+      <c r="B22" t="s">
+        <v>402</v>
+      </c>
+      <c r="C22" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" t="s">
+        <v>363</v>
+      </c>
+      <c r="E22" t="s">
+        <v>404</v>
+      </c>
+      <c r="F22" t="s">
+        <v>405</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>407</v>
+      </c>
+      <c r="B23" t="s">
+        <v>408</v>
+      </c>
+      <c r="C23" t="s">
+        <v>409</v>
+      </c>
+      <c r="D23" t="s">
+        <v>299</v>
+      </c>
+      <c r="E23" t="s">
+        <v>410</v>
+      </c>
+      <c r="F23" t="s">
+        <v>411</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>413</v>
+      </c>
+      <c r="B24" t="s">
+        <v>414</v>
+      </c>
+      <c r="C24" t="s">
+        <v>415</v>
+      </c>
+      <c r="D24" t="s">
+        <v>328</v>
+      </c>
+      <c r="E24" t="s">
+        <v>416</v>
+      </c>
+      <c r="F24" t="s">
+        <v>417</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>419</v>
+      </c>
+      <c r="B25" t="s">
+        <v>322</v>
+      </c>
+      <c r="C25" t="s">
+        <v>420</v>
+      </c>
+      <c r="D25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25" t="s">
+        <v>421</v>
+      </c>
+      <c r="F25" t="s">
+        <v>324</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>423</v>
+      </c>
+      <c r="B26" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" t="s">
+        <v>425</v>
+      </c>
+      <c r="D26" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26" t="s">
+        <v>426</v>
+      </c>
+      <c r="F26" t="s">
+        <v>427</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>429</v>
+      </c>
+      <c r="C27" t="s">
+        <v>430</v>
+      </c>
+      <c r="D27" t="s">
+        <v>299</v>
+      </c>
+      <c r="E27" t="s">
+        <v>431</v>
+      </c>
+      <c r="F27" t="s">
+        <v>432</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>434</v>
+      </c>
+      <c r="B28" t="s">
+        <v>435</v>
+      </c>
+      <c r="C28" t="s">
+        <v>436</v>
+      </c>
+      <c r="D28" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28" t="s">
+        <v>437</v>
+      </c>
+      <c r="F28" t="s">
+        <v>301</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>439</v>
+      </c>
+      <c r="B29" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" t="s">
+        <v>311</v>
+      </c>
+      <c r="D29" t="s">
+        <v>299</v>
+      </c>
+      <c r="E29" t="s">
+        <v>440</v>
+      </c>
+      <c r="F29" t="s">
+        <v>358</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>442</v>
+      </c>
+      <c r="B30" t="s">
+        <v>443</v>
+      </c>
+      <c r="C30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" t="s">
+        <v>299</v>
+      </c>
+      <c r="E30" t="s">
+        <v>444</v>
+      </c>
+      <c r="F30" t="s">
+        <v>445</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>447</v>
+      </c>
+      <c r="B31" t="s">
+        <v>448</v>
+      </c>
+      <c r="C31" t="s">
+        <v>305</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" t="s">
+        <v>449</v>
+      </c>
+      <c r="F31" t="s">
+        <v>450</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>452</v>
+      </c>
+      <c r="B32" t="s">
+        <v>453</v>
+      </c>
+      <c r="C32" t="s">
+        <v>305</v>
+      </c>
+      <c r="D32" t="s">
+        <v>363</v>
+      </c>
+      <c r="E32" t="s">
+        <v>454</v>
+      </c>
+      <c r="F32" t="s">
+        <v>455</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>457</v>
+      </c>
+      <c r="B33" t="s">
+        <v>458</v>
+      </c>
+      <c r="C33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D33" t="s">
+        <v>328</v>
+      </c>
+      <c r="E33" t="s">
+        <v>460</v>
+      </c>
+      <c r="F33" t="s">
+        <v>461</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>463</v>
+      </c>
+      <c r="B34" t="s">
+        <v>464</v>
+      </c>
+      <c r="C34" t="s">
+        <v>465</v>
+      </c>
+      <c r="D34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E34" t="s">
+        <v>399</v>
+      </c>
+      <c r="F34" t="s">
+        <v>394</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>467</v>
+      </c>
+      <c r="B35" t="s">
+        <v>468</v>
+      </c>
+      <c r="C35" t="s">
+        <v>469</v>
+      </c>
+      <c r="D35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E35" t="s">
+        <v>470</v>
+      </c>
+      <c r="F35" t="s">
+        <v>471</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>473</v>
+      </c>
+      <c r="B36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C36" t="s">
+        <v>475</v>
+      </c>
+      <c r="D36" t="s">
+        <v>299</v>
+      </c>
+      <c r="E36" t="s">
+        <v>476</v>
+      </c>
+      <c r="F36" t="s">
+        <v>477</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>479</v>
+      </c>
+      <c r="B37" t="s">
+        <v>480</v>
+      </c>
+      <c r="C37" t="s">
+        <v>311</v>
+      </c>
+      <c r="D37" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" t="s">
+        <v>481</v>
+      </c>
+      <c r="F37" t="s">
+        <v>358</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>483</v>
+      </c>
+      <c r="B38" t="s">
+        <v>484</v>
+      </c>
+      <c r="C38" t="s">
+        <v>305</v>
+      </c>
+      <c r="D38" t="s">
+        <v>392</v>
+      </c>
+      <c r="E38" t="s">
+        <v>485</v>
+      </c>
+      <c r="F38" t="s">
+        <v>486</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>488</v>
+      </c>
+      <c r="B39" t="s">
+        <v>489</v>
+      </c>
+      <c r="C39" t="s">
+        <v>362</v>
+      </c>
+      <c r="D39" t="s">
+        <v>299</v>
+      </c>
+      <c r="E39" t="s">
+        <v>490</v>
+      </c>
+      <c r="F39" t="s">
+        <v>491</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>493</v>
+      </c>
+      <c r="B40" t="s">
+        <v>494</v>
+      </c>
+      <c r="C40" t="s">
+        <v>311</v>
+      </c>
+      <c r="D40" t="s">
+        <v>299</v>
+      </c>
+      <c r="E40" t="s">
+        <v>421</v>
+      </c>
+      <c r="F40" t="s">
+        <v>382</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>496</v>
+      </c>
+      <c r="B41" t="s">
+        <v>497</v>
+      </c>
+      <c r="C41" t="s">
+        <v>311</v>
+      </c>
+      <c r="D41" t="s">
+        <v>299</v>
+      </c>
+      <c r="E41" t="s">
+        <v>498</v>
+      </c>
+      <c r="F41" t="s">
+        <v>301</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>500</v>
+      </c>
+      <c r="B42" t="s">
+        <v>501</v>
+      </c>
+      <c r="C42" t="s">
+        <v>305</v>
+      </c>
+      <c r="D42" t="s">
+        <v>312</v>
+      </c>
+      <c r="E42" t="s">
+        <v>502</v>
+      </c>
+      <c r="F42" t="s">
+        <v>503</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>505</v>
+      </c>
+      <c r="B43" t="s">
+        <v>506</v>
+      </c>
+      <c r="C43" t="s">
+        <v>507</v>
+      </c>
+      <c r="D43" t="s">
+        <v>328</v>
+      </c>
+      <c r="E43" t="s">
+        <v>508</v>
+      </c>
+      <c r="F43" t="s">
+        <v>509</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>511</v>
+      </c>
+      <c r="B44" t="s">
+        <v>512</v>
+      </c>
+      <c r="C44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D44" t="s">
+        <v>299</v>
+      </c>
+      <c r="E44" t="s">
+        <v>513</v>
+      </c>
+      <c r="F44" t="s">
+        <v>399</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>515</v>
+      </c>
+      <c r="B45" t="s">
+        <v>516</v>
+      </c>
+      <c r="C45" t="s">
+        <v>517</v>
+      </c>
+      <c r="D45" t="s">
+        <v>299</v>
+      </c>
+      <c r="E45" t="s">
+        <v>518</v>
+      </c>
+      <c r="F45" t="s">
+        <v>519</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>521</v>
+      </c>
+      <c r="B46" t="s">
+        <v>522</v>
+      </c>
+      <c r="C46" t="s">
+        <v>305</v>
+      </c>
+      <c r="D46" t="s">
+        <v>392</v>
+      </c>
+      <c r="E46" t="s">
+        <v>523</v>
+      </c>
+      <c r="F46" t="s">
+        <v>524</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>526</v>
+      </c>
+      <c r="B47" t="s">
+        <v>527</v>
+      </c>
+      <c r="C47" t="s">
+        <v>298</v>
+      </c>
+      <c r="D47" t="s">
+        <v>299</v>
+      </c>
+      <c r="E47" t="s">
+        <v>528</v>
+      </c>
+      <c r="F47" t="s">
+        <v>399</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>530</v>
+      </c>
+      <c r="B48" t="s">
+        <v>531</v>
+      </c>
+      <c r="C48" t="s">
+        <v>305</v>
+      </c>
+      <c r="D48" t="s">
+        <v>299</v>
+      </c>
+      <c r="E48" t="s">
+        <v>532</v>
+      </c>
+      <c r="F48" t="s">
+        <v>533</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>535</v>
+      </c>
+      <c r="B49" t="s">
+        <v>536</v>
+      </c>
+      <c r="C49" t="s">
+        <v>298</v>
+      </c>
+      <c r="D49" t="s">
+        <v>299</v>
+      </c>
+      <c r="E49" t="s">
+        <v>537</v>
+      </c>
+      <c r="F49" t="s">
+        <v>491</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>539</v>
+      </c>
+      <c r="B50" t="s">
+        <v>540</v>
+      </c>
+      <c r="C50" t="s">
+        <v>541</v>
+      </c>
+      <c r="D50" t="s">
+        <v>328</v>
+      </c>
+      <c r="E50" t="s">
+        <v>542</v>
+      </c>
+      <c r="F50" t="s">
+        <v>543</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>545</v>
+      </c>
+      <c r="B51" t="s">
+        <v>546</v>
+      </c>
+      <c r="C51" t="s">
+        <v>362</v>
+      </c>
+      <c r="D51" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" t="s">
+        <v>547</v>
+      </c>
+      <c r="F51" t="s">
+        <v>548</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>550</v>
+      </c>
+      <c r="B52" t="s">
+        <v>551</v>
+      </c>
+      <c r="C52" t="s">
+        <v>552</v>
+      </c>
+      <c r="D52" t="s">
+        <v>299</v>
+      </c>
+      <c r="E52" t="s">
+        <v>553</v>
+      </c>
+      <c r="F52" t="s">
+        <v>554</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>556</v>
+      </c>
+      <c r="B53" t="s">
+        <v>557</v>
+      </c>
+      <c r="C53" t="s">
+        <v>558</v>
+      </c>
+      <c r="D53" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" t="s">
+        <v>559</v>
+      </c>
+      <c r="F53" t="s">
+        <v>560</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>562</v>
+      </c>
+      <c r="B54" t="s">
+        <v>380</v>
+      </c>
+      <c r="C54" t="s">
+        <v>229</v>
+      </c>
+      <c r="D54" t="s">
+        <v>299</v>
+      </c>
+      <c r="E54" t="s">
+        <v>563</v>
+      </c>
+      <c r="F54" t="s">
+        <v>382</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>565</v>
+      </c>
+      <c r="B55" t="s">
+        <v>566</v>
+      </c>
+      <c r="C55" t="s">
+        <v>567</v>
+      </c>
+      <c r="D55" t="s">
+        <v>299</v>
+      </c>
+      <c r="E55" t="s">
+        <v>568</v>
+      </c>
+      <c r="F55" t="s">
+        <v>569</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>571</v>
+      </c>
+      <c r="B56" t="s">
+        <v>572</v>
+      </c>
+      <c r="C56" t="s">
+        <v>573</v>
+      </c>
+      <c r="D56" t="s">
+        <v>299</v>
+      </c>
+      <c r="E56" t="s">
+        <v>574</v>
+      </c>
+      <c r="F56" t="s">
+        <v>575</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>577</v>
+      </c>
+      <c r="B57" t="s">
+        <v>578</v>
+      </c>
+      <c r="C57" t="s">
+        <v>311</v>
+      </c>
+      <c r="D57" t="s">
+        <v>299</v>
+      </c>
+      <c r="E57" t="s">
+        <v>579</v>
+      </c>
+      <c r="F57" t="s">
+        <v>580</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>582</v>
+      </c>
+      <c r="B58" t="s">
+        <v>583</v>
+      </c>
+      <c r="C58" t="s">
+        <v>558</v>
+      </c>
+      <c r="D58" t="s">
+        <v>299</v>
+      </c>
+      <c r="E58" t="s">
+        <v>584</v>
+      </c>
+      <c r="F58" t="s">
+        <v>394</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>586</v>
+      </c>
+      <c r="B59" t="s">
+        <v>587</v>
+      </c>
+      <c r="C59" t="s">
+        <v>305</v>
+      </c>
+      <c r="D59" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" t="s">
+        <v>588</v>
+      </c>
+      <c r="F59" t="s">
+        <v>301</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>590</v>
+      </c>
+      <c r="B60" t="s">
+        <v>591</v>
+      </c>
+      <c r="C60" t="s">
+        <v>305</v>
+      </c>
+      <c r="D60" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" t="s">
+        <v>592</v>
+      </c>
+      <c r="F60" t="s">
+        <v>593</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>595</v>
+      </c>
+      <c r="B61" t="s">
+        <v>596</v>
+      </c>
+      <c r="C61" t="s">
+        <v>311</v>
+      </c>
+      <c r="D61" t="s">
+        <v>299</v>
+      </c>
+      <c r="E61" t="s">
+        <v>597</v>
+      </c>
+      <c r="F61" t="s">
+        <v>598</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>600</v>
+      </c>
+      <c r="B62" t="s">
+        <v>322</v>
+      </c>
+      <c r="C62" t="s">
+        <v>305</v>
+      </c>
+      <c r="D62" t="s">
+        <v>299</v>
+      </c>
+      <c r="E62" t="s">
+        <v>601</v>
+      </c>
+      <c r="F62" t="s">
+        <v>399</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>603</v>
+      </c>
+      <c r="B63" t="s">
+        <v>604</v>
+      </c>
+      <c r="C63" t="s">
+        <v>305</v>
+      </c>
+      <c r="D63" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" t="s">
+        <v>605</v>
+      </c>
+      <c r="F63" t="s">
+        <v>606</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>608</v>
+      </c>
+      <c r="B64" t="s">
+        <v>474</v>
+      </c>
+      <c r="C64" t="s">
+        <v>475</v>
+      </c>
+      <c r="D64" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" t="s">
+        <v>609</v>
+      </c>
+      <c r="F64" t="s">
+        <v>477</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>611</v>
+      </c>
+      <c r="B65" t="s">
+        <v>612</v>
+      </c>
+      <c r="C65" t="s">
+        <v>613</v>
+      </c>
+      <c r="D65" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" t="s">
+        <v>614</v>
+      </c>
+      <c r="F65" t="s">
+        <v>615</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>617</v>
+      </c>
+      <c r="B66" t="s">
+        <v>591</v>
+      </c>
+      <c r="C66" t="s">
+        <v>305</v>
+      </c>
+      <c r="D66" t="s">
+        <v>299</v>
+      </c>
+      <c r="E66" t="s">
+        <v>618</v>
+      </c>
+      <c r="F66" t="s">
+        <v>593</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>620</v>
+      </c>
+      <c r="B67" t="s">
+        <v>621</v>
+      </c>
+      <c r="C67" t="s">
+        <v>622</v>
+      </c>
+      <c r="D67" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" t="s">
+        <v>623</v>
+      </c>
+      <c r="F67" t="s">
+        <v>624</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>626</v>
+      </c>
+      <c r="B68" t="s">
+        <v>627</v>
+      </c>
+      <c r="C68" t="s">
+        <v>628</v>
+      </c>
+      <c r="D68" t="s">
+        <v>363</v>
+      </c>
+      <c r="E68" t="s">
+        <v>629</v>
+      </c>
+      <c r="F68" t="s">
+        <v>630</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>237</v>
+      </c>
+      <c r="B69" t="s">
+        <v>632</v>
+      </c>
+      <c r="C69" t="s">
+        <v>311</v>
+      </c>
+      <c r="D69" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" t="s">
+        <v>633</v>
+      </c>
+      <c r="F69" t="s">
+        <v>634</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>237</v>
+      </c>
+      <c r="B70" t="s">
+        <v>636</v>
+      </c>
+      <c r="C70" t="s">
+        <v>637</v>
+      </c>
+      <c r="D70" t="s">
+        <v>299</v>
+      </c>
+      <c r="E70" t="s">
+        <v>638</v>
+      </c>
+      <c r="F70" t="s">
+        <v>639</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>641</v>
+      </c>
+      <c r="B71" t="s">
+        <v>642</v>
+      </c>
+      <c r="C71" t="s">
+        <v>541</v>
+      </c>
+      <c r="D71" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" t="s">
+        <v>643</v>
+      </c>
+      <c r="F71" t="s">
+        <v>644</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>646</v>
+      </c>
+      <c r="B72" t="s">
+        <v>647</v>
+      </c>
+      <c r="C72" t="s">
+        <v>298</v>
+      </c>
+      <c r="D72" t="s">
+        <v>299</v>
+      </c>
+      <c r="E72" t="s">
+        <v>648</v>
+      </c>
+      <c r="F72" t="s">
+        <v>649</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>651</v>
+      </c>
+      <c r="B73" t="s">
+        <v>652</v>
+      </c>
+      <c r="C73" t="s">
+        <v>311</v>
+      </c>
+      <c r="D73" t="s">
+        <v>299</v>
+      </c>
+      <c r="E73" t="s">
+        <v>653</v>
+      </c>
+      <c r="F73" t="s">
+        <v>399</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-21.xlsx
+++ b/docs/xlsx/jobs-2026-09-21.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="769">
   <si>
     <t>Title</t>
   </si>
@@ -943,6 +943,45 @@
     <t>https://www.idealist.org/en/consultant-job/1ee504c7aeba4bcd8d38de3940afe9cf-account-manager-direct-mail-missionwired-washington</t>
   </si>
   <si>
+    <t>Accounting Manager</t>
+  </si>
+  <si>
+    <t>Asian Law Caucus</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 101480.00 - 114223.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/965b871221644699a279ceb8eeabe88a-accounting-manager-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>Administrative Assistant</t>
+  </si>
+  <si>
+    <t>Play Mountain Place</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 25.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c01d286cbb664d28b0952840c4cff10f-administrative-assistant-play-mountain-place-los-angeles</t>
+  </si>
+  <si>
     <t>Administrative Assistant - Autumn, Winter, &amp; Spring Saturday Academy (Part-time)</t>
   </si>
   <si>
@@ -1000,9 +1039,6 @@
     <t>The YWCA of the City of New York</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>USD 20.00 - 24.00/hour</t>
   </si>
   <si>
@@ -1117,6 +1153,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/ed01cebfe4e947eb91d54de61ce38f0a-chofer-medicos-del-mundo-suiza-mision-mexico-ciudad-de-mexico</t>
   </si>
   <si>
+    <t>Cluster Director – South America | Plan International</t>
+  </si>
+  <si>
+    <t>Consultoría Aplicada</t>
+  </si>
+  <si>
+    <t>Remote (EC)</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Women, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/b6da41c116574f45a09893bac71895ca-cluster-director-south-america-plan-international-consultoria-aplicada-tegucigalpa</t>
+  </si>
+  <si>
+    <t>Remote (PE)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/786c61c8c70b4261aa8ec013006b53c8-cluster-director-south-america-plan-international-consultoria-aplicada-tegucigalpa</t>
+  </si>
+  <si>
+    <t>Remote (PY)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/4e41d476d5f74de9a3ff0c6149326296-cluster-director-south-america-plan-international-consultoria-aplicada-tegucigalpa</t>
+  </si>
+  <si>
     <t>Communications &amp; Social Media Coordinator</t>
   </si>
   <si>
@@ -1162,9 +1228,6 @@
     <t>USD 22.00 - 26.00/hour</t>
   </si>
   <si>
-    <t>Children Youth, Education, Family</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/ee4624dc9cb34f65993a5e7c8f488e40-community-operations-coordinator-united-south-end-settlements-boston</t>
   </si>
   <si>
@@ -1255,6 +1318,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/aa5e5d2c8aad4d198651587eaf5ea402-coordinator-total-rewards-national-geographic-society-washington</t>
   </si>
   <si>
+    <t>Data &amp; IT Coordinator</t>
+  </si>
+  <si>
+    <t>All In Energy</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 28.88 - 28.88/hour</t>
+  </si>
+  <si>
+    <t>Climate Change, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/94bc95ff17fa4a079a3acc6ce48adc4d-data-it-coordinator-all-in-energy-brookline</t>
+  </si>
+  <si>
     <t>Database and Development Coordinator</t>
   </si>
   <si>
@@ -1273,6 +1354,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/78caed167db94989834d48f8c82e7364-database-and-development-coordinator-ecumenical-ministries-of-oregon-portland</t>
   </si>
   <si>
+    <t>Development Assistant</t>
+  </si>
+  <si>
+    <t>Baby2Baby</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8eb15fd152334414a851d5265a3b6a92-development-assistant-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Development Director</t>
+  </si>
+  <si>
+    <t>Kentucky Refugee Ministries, Inc.</t>
+  </si>
+  <si>
+    <t>Louisville, KY</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d6313d9d8db74bd0be4509470c8ac00a-development-director-kentucky-refugee-ministries-inc-louisville</t>
+  </si>
+  <si>
     <t>Development Manager, New York Chapter</t>
   </si>
   <si>
@@ -1285,6 +1396,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/4411f20ae1a0459f907352cf74d35082-development-manager-new-york-chapter-parkinsons-foundation-rochester</t>
   </si>
   <si>
+    <t>Digital Communications Manager</t>
+  </si>
+  <si>
+    <t>Center for Tech and Civic Life</t>
+  </si>
+  <si>
+    <t>USD 82340.51 - 90129.99/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Communications Access, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/05d3f50cbc724b9797376b42a4d1667d-digital-communications-manager-center-for-tech-and-civic-life-chicago</t>
+  </si>
+  <si>
     <t>Director (a) de Conservación e Investigación</t>
   </si>
   <si>
@@ -1306,9 +1432,6 @@
     <t>The Redford Center</t>
   </si>
   <si>
-    <t>San Francisco, California</t>
-  </si>
-  <si>
     <t>USD 125000.00 - 130000.00/year</t>
   </si>
   <si>
@@ -1342,6 +1465,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/d7c77afbfbe14afeb1e2730963fd4f86-director-of-social-services-urban-pathways-new-york</t>
   </si>
   <si>
+    <t>Director, Development Operations</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 145000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ad0a5518332545a89e4f443b5ba2b934-director-development-operations-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Director, Global Food Sovereignty Movements Program</t>
   </si>
   <si>
@@ -1417,6 +1549,60 @@
     <t>https://www.idealist.org/en/nonprofit-job/970dd34cd2c644b486597b04e436f54a-especialista-de-lingua-portuguesa-fundacao-geniantis-sao-paulo</t>
   </si>
   <si>
+    <t>Europe Programme Officer - Balkans</t>
+  </si>
+  <si>
+    <t>International Detention Coalition</t>
+  </si>
+  <si>
+    <t>Remote (BA)</t>
+  </si>
+  <si>
+    <t>EUR 30000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffaa4cb45a084dc5a25bc0cedd6c27c2-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (MK)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e326caa4c5e549d08d714cd0ae2c942c-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (RS)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ac5bcae02a4040f0a9b1f395fdec048f-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (ME)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a542d03048c04e01985c2812f2daa2cf-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (AL)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/68bcac26676f4777a071fe501e27bda4-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (XK)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/478fb0a7063643009eaeb79cc79c7541-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
+    <t>Remote (GR)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24585e9c3af54b87bc1563a2b6d3cd4b-europe-programme-officer-balkans-international-detention-coalition-melbourne</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1435,6 +1621,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/f846957a398d47fdb242875b8fe6e24b-executive-director-sacred-threads-newton</t>
   </si>
   <si>
+    <t>Executive Director - Florida Diabetes Camp</t>
+  </si>
+  <si>
+    <t>Immersive1st</t>
+  </si>
+  <si>
+    <t>Gainesville, Florida</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/c84329c0be51467dbc473dc526cbfa56-executive-director-florida-diabetes-camp-immersive1st-gainesville</t>
+  </si>
+  <si>
     <t>Family Defense Unit Social Worker - White Plains</t>
   </si>
   <si>
@@ -1495,6 +1696,33 @@
     <t>https://www.idealist.org/en/nonprofit-job/cc92143d97ee4906870018bd2057ebbf-gerentea-de-captacion-y-recaudacion-de-fondos-world-vision-mexico-ciudad-de-mexico</t>
   </si>
   <si>
+    <t>Housing Rights Staff Attorney (or Senior Staff Attorney)</t>
+  </si>
+  <si>
+    <t>USD 87550.00 - 148629.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4399edabfe7d46d5bb81666e4a2242e2-housing-rights-staff-attorney-or-senior-staff-attorney-asian-law-caucus-san-francisco</t>
+  </si>
+  <si>
+    <t>HR &amp; Administrative Associate</t>
+  </si>
+  <si>
+    <t>iNaturalist</t>
+  </si>
+  <si>
+    <t>San Rafael, California</t>
+  </si>
+  <si>
+    <t>USD 70310.00 - 70310.00/year</t>
+  </si>
+  <si>
+    <t>Environment, Science Technology</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7ccb65356e3c45498119a2acb5f5cf25-hr-administrative-associate-inaturalist-san-rafael</t>
+  </si>
+  <si>
     <t>HR Talent Aquisition Associate</t>
   </si>
   <si>
@@ -1555,9 +1783,6 @@
     <t>TBF -The Boston Foundation</t>
   </si>
   <si>
-    <t>USD 75000.00 - 85000.00/year</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/3a3f87cd88ed46ac85abaaa7701a7ce7-impact-analyst-equitable-learning-measurement-tbf-the-boston-foundation-boston</t>
   </si>
   <si>
@@ -1594,6 +1819,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/b09f43dc456c4d0fa24f7fb1e86075d6-international-director-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Job Developer, Healthcare Workforce</t>
+  </si>
+  <si>
+    <t>Uplift Communities LLC</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Health Medicine, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/cc03c38244b247448e4d2278670689de-job-developer-healthcare-workforce-uplift-communities-llc-new-york</t>
+  </si>
+  <si>
     <t>Lead Street Outreach Case Manager</t>
   </si>
   <si>
@@ -1621,6 +1861,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/911d6003ad3843f8b1c43d5050a77669-leda-special-events-advancement-operations-officer-leda-leadership-enterprise-for-a-diverse-america-new-york</t>
   </si>
   <si>
+    <t>Line Producer (Gestão de processos)</t>
+  </si>
+  <si>
+    <t>instituto BR cultural</t>
+  </si>
+  <si>
+    <t>BRL 4300.00 - 4300.00/year</t>
+  </si>
+  <si>
+    <t>Communications Access, Education, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/dd8145f9e22d415ca106e4aafabdb853-line-producer-gestao-de-processos-instituto-br-cultural-sao-paulo</t>
+  </si>
+  <si>
     <t>Manager, Development</t>
   </si>
   <si>
@@ -1633,6 +1888,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/637a51a963e147f9a018d46c8f2473d3-manager-development-future-caucus-washington</t>
   </si>
   <si>
+    <t>Managing Attorney-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>Catholic Charities of Los Angeles, Inc</t>
+  </si>
+  <si>
+    <t>USD 70304.00 - 90271.00/year</t>
+  </si>
+  <si>
+    <t>Education, Housing Homelessness, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/42b61a1941c34b2ca8bc4c4661bbfb14-managing-attorney-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Metro Detroit Program Facilitator</t>
   </si>
   <si>
@@ -1684,6 +1954,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/e74553ce98b048d8a37ae04a76789f68-partnerships-manager-826nyc-kings-county</t>
   </si>
   <si>
+    <t>People Operations Manager (Benefits &amp; Payroll)</t>
+  </si>
+  <si>
+    <t>FreeWill</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 105000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/53de11d6345e4eae8eeaa0c91ed21a8a-people-operations-manager-benefits-payroll-freewill-new-york</t>
+  </si>
+  <si>
     <t>People Operations Specialist</t>
   </si>
   <si>
@@ -1702,6 +1987,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/c37fdaccec5d47f0b48d044b4e8d5835-people-operations-specialist-partners-for-sacred-places-philadelphia</t>
   </si>
   <si>
+    <t>Procurement Manager</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/59c205bdfd324af2ad9c62cab1499eae-procurement-manager-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Program Administration Coordinator</t>
   </si>
   <si>
@@ -1747,6 +2038,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/a48836e3d93c4f148d50149409991384-program-coordinator-continuing-education-american-society-of-clinical-oncology-alexandria</t>
   </si>
   <si>
+    <t>Program Manager - Minnesota</t>
+  </si>
+  <si>
+    <t>Reading Partners</t>
+  </si>
+  <si>
+    <t>Saint Paul, Minnesota</t>
+  </si>
+  <si>
+    <t>USD 60650.00 - 71753.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8509f917f75b4370b4277abea2bd607b-program-manager-minnesota-reading-partners-saint-paul</t>
+  </si>
+  <si>
     <t>Program Operations Associate, Conservation Innovation</t>
   </si>
   <si>
@@ -1876,6 +2182,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/a285905d8a2544309d09424f5c3843c7-senior-salesforce-administrator-and-business-analyst-coefficient-giving-san-francisco</t>
   </si>
   <si>
+    <t>Senior Shipping Coordinator (Contract)</t>
+  </si>
+  <si>
+    <t>USD 24.00 - 30.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/287a8b1dfbe04c86bd798c9716a41664-senior-shipping-coordinator-contract-baby2baby-los-angeles</t>
+  </si>
+  <si>
     <t>Social Enterprise &amp; Youth Development Manager</t>
   </si>
   <si>
@@ -1927,9 +2242,6 @@
     <t>Immigration Center for Women and Children</t>
   </si>
   <si>
-    <t>Los Angeles, California</t>
-  </si>
-  <si>
     <t>USD 78000.00 - 95000.00/year</t>
   </si>
   <si>
@@ -1939,6 +2251,12 @@
     <t>https://www.idealist.org/en/nonprofit-job/bc95ecc7ea574742be0fe0ee2409fd98-staff-attorney-immigration-center-for-women-and-children-los-angeles</t>
   </si>
   <si>
+    <t>Staff Attorney II-Esperanza Immigrant Rights Project</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34a1e3144a014d078a56226edbddc4b3-staff-attorney-ii-esperanza-immigrant-rights-project-catholic-charities-of-los-angeles-inc-los-angeles</t>
+  </si>
+  <si>
     <t>Support Coordinator</t>
   </si>
   <si>
@@ -1967,6 +2285,30 @@
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/39d44c37065247d68023cf114a4ae45b-vice-president-government-relations-political-affairs-league-of-conservation-voters-washington</t>
+  </si>
+  <si>
+    <t>VP, Marketing &amp; Communications</t>
+  </si>
+  <si>
+    <t>USD 180000.00 - 200000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9545c9f548374e7eb974c885482ff028-vp-marketing-communications-baby2baby-los-angeles</t>
+  </si>
+  <si>
+    <t>Warehouse Coordinator</t>
+  </si>
+  <si>
+    <t>Alameda Food Bank</t>
+  </si>
+  <si>
+    <t>USD 30.16 - 30.16/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security, Poverty, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7705a91fead8431fa768f58ea59469c9-warehouse-coordinator-alameda-food-bank-alameda</t>
   </si>
   <si>
     <t>Workers' Rights Organizer - Temporary</t>
@@ -3830,7 +4172,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -3926,13 +4268,13 @@
         <v>311</v>
       </c>
       <c r="D4" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" t="s">
         <v>312</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>313</v>
-      </c>
-      <c r="F4" t="s">
-        <v>301</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>314</v>
@@ -3949,243 +4291,243 @@
         <v>317</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="E5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C6" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D6" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="E6" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F6" t="s">
-        <v>324</v>
+        <v>301</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="D7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C8" t="s">
-        <v>334</v>
+        <v>305</v>
       </c>
       <c r="D8" t="s">
         <v>299</v>
       </c>
       <c r="E8" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F8" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C9" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="D9" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B11" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C11" t="s">
-        <v>349</v>
+        <v>263</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E11" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B12" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C12" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="E12" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F12" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B13" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C13" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="E13" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="F13" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B14" t="s">
         <v>356</v>
       </c>
       <c r="C14" t="s">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="D14" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="E14" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="F14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B15" t="s">
+        <v>356</v>
+      </c>
+      <c r="C15" t="s">
         <v>361</v>
       </c>
-      <c r="C15" t="s">
-        <v>362</v>
-      </c>
       <c r="D15" t="s">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="E15" t="s">
         <v>364</v>
       </c>
       <c r="F15" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>366</v>
@@ -4199,33 +4541,33 @@
         <v>368</v>
       </c>
       <c r="C16" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" t="s">
+        <v>299</v>
+      </c>
+      <c r="E16" t="s">
         <v>369</v>
       </c>
-      <c r="D16" t="s">
-        <v>328</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>370</v>
       </c>
-      <c r="F16" t="s">
+      <c r="H16" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>372</v>
+      </c>
+      <c r="B17" t="s">
         <v>373</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>374</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>375</v>
-      </c>
-      <c r="D17" t="s">
-        <v>299</v>
       </c>
       <c r="E17" t="s">
         <v>376</v>
@@ -4245,1284 +4587,1974 @@
         <v>380</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>381</v>
       </c>
       <c r="D18" t="s">
         <v>299</v>
       </c>
       <c r="E18" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F18" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="B19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C19" t="s">
         <v>385</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>299</v>
+      </c>
+      <c r="E19" t="s">
+        <v>382</v>
+      </c>
+      <c r="F19" t="s">
+        <v>383</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="D19" t="s">
-        <v>299</v>
-      </c>
-      <c r="E19" t="s">
-        <v>387</v>
-      </c>
-      <c r="F19" t="s">
-        <v>388</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="B20" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="C20" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="D20" t="s">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="E20" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="F20" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="C21" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="D21" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E21" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="F21" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B22" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C22" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="D22" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="E22" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F22" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B23" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C23" t="s">
-        <v>409</v>
+        <v>229</v>
       </c>
       <c r="D23" t="s">
         <v>299</v>
       </c>
       <c r="E23" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="F23" t="s">
-        <v>411</v>
+        <v>320</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B24" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="C24" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="D24" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E24" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F24" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B25" t="s">
-        <v>322</v>
+        <v>412</v>
       </c>
       <c r="C25" t="s">
-        <v>420</v>
+        <v>305</v>
       </c>
       <c r="D25" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="E25" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="F25" t="s">
-        <v>324</v>
+        <v>415</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B26" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C26" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D26" t="s">
         <v>299</v>
       </c>
       <c r="E26" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F26" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>422</v>
       </c>
       <c r="B27" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C27" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D27" t="s">
-        <v>299</v>
+        <v>375</v>
       </c>
       <c r="E27" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F27" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="B28" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C28" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="D28" t="s">
         <v>299</v>
       </c>
       <c r="E28" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="F28" t="s">
-        <v>301</v>
+        <v>432</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>434</v>
+      </c>
+      <c r="B29" t="s">
+        <v>435</v>
+      </c>
+      <c r="C29" t="s">
+        <v>436</v>
+      </c>
+      <c r="D29" t="s">
+        <v>299</v>
+      </c>
+      <c r="E29" t="s">
+        <v>437</v>
+      </c>
+      <c r="F29" t="s">
+        <v>438</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="B29" t="s">
-        <v>356</v>
-      </c>
-      <c r="C29" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" t="s">
-        <v>299</v>
-      </c>
-      <c r="E29" t="s">
-        <v>440</v>
-      </c>
-      <c r="F29" t="s">
-        <v>358</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>440</v>
+      </c>
+      <c r="B30" t="s">
+        <v>441</v>
+      </c>
+      <c r="C30" t="s">
         <v>442</v>
       </c>
-      <c r="B30" t="s">
+      <c r="D30" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" t="s">
         <v>443</v>
       </c>
-      <c r="C30" t="s">
-        <v>305</v>
-      </c>
-      <c r="D30" t="s">
-        <v>299</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>444</v>
       </c>
-      <c r="F30" t="s">
+      <c r="H30" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B31" t="s">
         <v>447</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>317</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31" t="s">
+        <v>403</v>
+      </c>
+      <c r="F31" t="s">
         <v>448</v>
       </c>
-      <c r="C31" t="s">
-        <v>305</v>
-      </c>
-      <c r="D31" t="s">
-        <v>299</v>
-      </c>
-      <c r="E31" t="s">
+      <c r="H31" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F31" t="s">
-        <v>450</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>450</v>
+      </c>
+      <c r="B32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C32" t="s">
         <v>452</v>
       </c>
-      <c r="B32" t="s">
+      <c r="D32" t="s">
+        <v>299</v>
+      </c>
+      <c r="E32" t="s">
         <v>453</v>
       </c>
-      <c r="C32" t="s">
-        <v>305</v>
-      </c>
-      <c r="D32" t="s">
-        <v>363</v>
-      </c>
-      <c r="E32" t="s">
+      <c r="F32" t="s">
         <v>454</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>456</v>
+      </c>
+      <c r="B33" t="s">
+        <v>335</v>
+      </c>
+      <c r="C33" t="s">
         <v>457</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
+        <v>299</v>
+      </c>
+      <c r="E33" t="s">
         <v>458</v>
       </c>
-      <c r="C33" t="s">
+      <c r="F33" t="s">
+        <v>337</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="D33" t="s">
-        <v>328</v>
-      </c>
-      <c r="E33" t="s">
-        <v>460</v>
-      </c>
-      <c r="F33" t="s">
-        <v>461</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>460</v>
+      </c>
+      <c r="B34" t="s">
+        <v>461</v>
+      </c>
+      <c r="C34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D34" t="s">
+        <v>299</v>
+      </c>
+      <c r="E34" t="s">
+        <v>462</v>
+      </c>
+      <c r="F34" t="s">
         <v>463</v>
       </c>
-      <c r="B34" t="s">
+      <c r="H34" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="C34" t="s">
-        <v>465</v>
-      </c>
-      <c r="D34" t="s">
-        <v>299</v>
-      </c>
-      <c r="E34" t="s">
-        <v>399</v>
-      </c>
-      <c r="F34" t="s">
-        <v>394</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>465</v>
+      </c>
+      <c r="B35" t="s">
+        <v>466</v>
+      </c>
+      <c r="C35" t="s">
         <v>467</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
+        <v>299</v>
+      </c>
+      <c r="E35" t="s">
         <v>468</v>
       </c>
-      <c r="C35" t="s">
+      <c r="F35" t="s">
         <v>469</v>
       </c>
-      <c r="D35" t="s">
-        <v>328</v>
-      </c>
-      <c r="E35" t="s">
+      <c r="H35" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="F35" t="s">
-        <v>471</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B36" t="s">
+        <v>471</v>
+      </c>
+      <c r="C36" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" t="s">
+        <v>299</v>
+      </c>
+      <c r="E36" t="s">
+        <v>472</v>
+      </c>
+      <c r="F36" t="s">
         <v>473</v>
       </c>
-      <c r="B36" t="s">
+      <c r="H36" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="C36" t="s">
-        <v>475</v>
-      </c>
-      <c r="D36" t="s">
-        <v>299</v>
-      </c>
-      <c r="E36" t="s">
-        <v>476</v>
-      </c>
-      <c r="F36" t="s">
-        <v>477</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>475</v>
+      </c>
+      <c r="B37" t="s">
+        <v>476</v>
+      </c>
+      <c r="C37" t="s">
+        <v>477</v>
+      </c>
+      <c r="D37" t="s">
+        <v>299</v>
+      </c>
+      <c r="E37" t="s">
+        <v>478</v>
+      </c>
+      <c r="F37" t="s">
+        <v>301</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="B37" t="s">
-        <v>480</v>
-      </c>
-      <c r="C37" t="s">
-        <v>311</v>
-      </c>
-      <c r="D37" t="s">
-        <v>299</v>
-      </c>
-      <c r="E37" t="s">
-        <v>481</v>
-      </c>
-      <c r="F37" t="s">
-        <v>358</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B38" t="s">
-        <v>484</v>
+        <v>368</v>
       </c>
       <c r="C38" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D38" t="s">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="E38" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="F38" t="s">
-        <v>486</v>
+        <v>370</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B39" t="s">
-        <v>489</v>
+        <v>447</v>
       </c>
       <c r="C39" t="s">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="D39" t="s">
         <v>299</v>
       </c>
       <c r="E39" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="F39" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
       <c r="B40" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="C40" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D40" t="s">
         <v>299</v>
       </c>
       <c r="E40" t="s">
-        <v>421</v>
+        <v>488</v>
       </c>
       <c r="F40" t="s">
-        <v>382</v>
+        <v>489</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B41" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="C41" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D41" t="s">
         <v>299</v>
       </c>
       <c r="E41" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F41" t="s">
-        <v>301</v>
+        <v>494</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B42" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C42" t="s">
         <v>305</v>
       </c>
       <c r="D42" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="E42" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F42" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>501</v>
+      </c>
+      <c r="B43" t="s">
+        <v>502</v>
+      </c>
+      <c r="C43" t="s">
+        <v>503</v>
+      </c>
+      <c r="D43" t="s">
+        <v>318</v>
+      </c>
+      <c r="E43" t="s">
+        <v>504</v>
+      </c>
+      <c r="F43" t="s">
         <v>505</v>
       </c>
-      <c r="B43" t="s">
+      <c r="H43" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="C43" t="s">
-        <v>507</v>
-      </c>
-      <c r="D43" t="s">
-        <v>328</v>
-      </c>
-      <c r="E43" t="s">
-        <v>508</v>
-      </c>
-      <c r="F43" t="s">
-        <v>509</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B44" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C44" t="s">
-        <v>334</v>
+        <v>509</v>
       </c>
       <c r="D44" t="s">
         <v>299</v>
       </c>
       <c r="E44" t="s">
-        <v>513</v>
+        <v>420</v>
       </c>
       <c r="F44" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>511</v>
+      </c>
+      <c r="B45" t="s">
+        <v>512</v>
+      </c>
+      <c r="C45" t="s">
+        <v>513</v>
+      </c>
+      <c r="D45" t="s">
+        <v>299</v>
+      </c>
+      <c r="E45" t="s">
+        <v>514</v>
+      </c>
+      <c r="F45" t="s">
         <v>515</v>
       </c>
-      <c r="B45" t="s">
+      <c r="H45" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C45" t="s">
-        <v>517</v>
-      </c>
-      <c r="D45" t="s">
-        <v>299</v>
-      </c>
-      <c r="E45" t="s">
-        <v>518</v>
-      </c>
-      <c r="F45" t="s">
-        <v>519</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="B46" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="C46" t="s">
-        <v>305</v>
+        <v>517</v>
       </c>
       <c r="D46" t="s">
-        <v>392</v>
+        <v>299</v>
       </c>
       <c r="E46" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="F46" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="B47" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="C47" t="s">
-        <v>298</v>
+        <v>519</v>
       </c>
       <c r="D47" t="s">
         <v>299</v>
       </c>
       <c r="E47" t="s">
-        <v>528</v>
+        <v>514</v>
       </c>
       <c r="F47" t="s">
-        <v>399</v>
+        <v>515</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="B48" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="C48" t="s">
-        <v>305</v>
+        <v>521</v>
       </c>
       <c r="D48" t="s">
         <v>299</v>
       </c>
       <c r="E48" t="s">
-        <v>532</v>
+        <v>514</v>
       </c>
       <c r="F48" t="s">
-        <v>533</v>
+        <v>515</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>535</v>
+        <v>511</v>
       </c>
       <c r="B49" t="s">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="C49" t="s">
-        <v>298</v>
+        <v>523</v>
       </c>
       <c r="D49" t="s">
         <v>299</v>
       </c>
       <c r="E49" t="s">
-        <v>537</v>
+        <v>514</v>
       </c>
       <c r="F49" t="s">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="B50" t="s">
-        <v>540</v>
+        <v>512</v>
       </c>
       <c r="C50" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="D50" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="E50" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="F50" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>544</v>
+        <v>526</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>545</v>
+        <v>511</v>
       </c>
       <c r="B51" t="s">
-        <v>546</v>
+        <v>512</v>
       </c>
       <c r="C51" t="s">
-        <v>362</v>
+        <v>527</v>
       </c>
       <c r="D51" t="s">
         <v>299</v>
       </c>
       <c r="E51" t="s">
-        <v>547</v>
+        <v>514</v>
       </c>
       <c r="F51" t="s">
-        <v>548</v>
+        <v>515</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="B52" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="C52" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="D52" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E52" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="F52" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="B53" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="C53" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="D53" t="s">
         <v>299</v>
       </c>
       <c r="E53" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="F53" t="s">
-        <v>560</v>
+        <v>448</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="B54" t="s">
-        <v>380</v>
+        <v>541</v>
       </c>
       <c r="C54" t="s">
-        <v>229</v>
+        <v>542</v>
       </c>
       <c r="D54" t="s">
         <v>299</v>
       </c>
       <c r="E54" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="F54" t="s">
-        <v>382</v>
+        <v>544</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="B55" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="C55" t="s">
-        <v>567</v>
+        <v>324</v>
       </c>
       <c r="D55" t="s">
         <v>299</v>
       </c>
       <c r="E55" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="F55" t="s">
-        <v>569</v>
+        <v>370</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="B56" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="C56" t="s">
-        <v>573</v>
+        <v>305</v>
       </c>
       <c r="D56" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="E56" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="F56" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="B57" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="C57" t="s">
-        <v>311</v>
+        <v>374</v>
       </c>
       <c r="D57" t="s">
         <v>299</v>
       </c>
       <c r="E57" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="F57" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>581</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="B58" t="s">
-        <v>583</v>
+        <v>310</v>
       </c>
       <c r="C58" t="s">
-        <v>558</v>
+        <v>311</v>
       </c>
       <c r="D58" t="s">
         <v>299</v>
       </c>
       <c r="E58" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="F58" t="s">
-        <v>394</v>
+        <v>313</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>585</v>
+        <v>562</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>586</v>
+        <v>563</v>
       </c>
       <c r="B59" t="s">
-        <v>587</v>
+        <v>564</v>
       </c>
       <c r="C59" t="s">
-        <v>305</v>
+        <v>565</v>
       </c>
       <c r="D59" t="s">
         <v>299</v>
       </c>
       <c r="E59" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="F59" t="s">
-        <v>301</v>
+        <v>567</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="B60" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="C60" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="D60" t="s">
         <v>299</v>
       </c>
       <c r="E60" t="s">
-        <v>592</v>
+        <v>458</v>
       </c>
       <c r="F60" t="s">
-        <v>593</v>
+        <v>320</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>594</v>
+        <v>571</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>595</v>
+        <v>572</v>
       </c>
       <c r="B61" t="s">
-        <v>596</v>
+        <v>573</v>
       </c>
       <c r="C61" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D61" t="s">
         <v>299</v>
       </c>
       <c r="E61" t="s">
-        <v>597</v>
+        <v>574</v>
       </c>
       <c r="F61" t="s">
-        <v>598</v>
+        <v>301</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B62" t="s">
-        <v>322</v>
+        <v>577</v>
       </c>
       <c r="C62" t="s">
         <v>305</v>
       </c>
       <c r="D62" t="s">
-        <v>299</v>
+        <v>325</v>
       </c>
       <c r="E62" t="s">
-        <v>601</v>
+        <v>578</v>
       </c>
       <c r="F62" t="s">
-        <v>399</v>
+        <v>579</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="B63" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="C63" t="s">
-        <v>305</v>
+        <v>583</v>
       </c>
       <c r="D63" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="E63" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="F63" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="B64" t="s">
-        <v>474</v>
+        <v>588</v>
       </c>
       <c r="C64" t="s">
-        <v>475</v>
+        <v>346</v>
       </c>
       <c r="D64" t="s">
         <v>299</v>
       </c>
       <c r="E64" t="s">
-        <v>609</v>
+        <v>453</v>
       </c>
       <c r="F64" t="s">
-        <v>477</v>
+        <v>420</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="B65" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="C65" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="D65" t="s">
         <v>299</v>
       </c>
       <c r="E65" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="F65" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="B66" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="C66" t="s">
         <v>305</v>
       </c>
       <c r="D66" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="E66" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
       <c r="F66" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="B67" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="C67" t="s">
-        <v>622</v>
+        <v>324</v>
       </c>
       <c r="D67" t="s">
         <v>299</v>
       </c>
       <c r="E67" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
       <c r="F67" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="B68" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="C68" t="s">
-        <v>628</v>
+        <v>298</v>
       </c>
       <c r="D68" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="E68" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="F68" t="s">
-        <v>630</v>
+        <v>420</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>631</v>
+        <v>609</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>237</v>
+        <v>610</v>
       </c>
       <c r="B69" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="C69" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="D69" t="s">
         <v>299</v>
       </c>
       <c r="E69" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="F69" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>237</v>
+        <v>615</v>
       </c>
       <c r="B70" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="C70" t="s">
-        <v>637</v>
+        <v>509</v>
       </c>
       <c r="D70" t="s">
-        <v>299</v>
+        <v>413</v>
       </c>
       <c r="E70" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="F70" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="B71" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="C71" t="s">
-        <v>541</v>
+        <v>298</v>
       </c>
       <c r="D71" t="s">
         <v>299</v>
       </c>
       <c r="E71" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="F71" t="s">
-        <v>644</v>
+        <v>558</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="B72" t="s">
-        <v>647</v>
+        <v>625</v>
       </c>
       <c r="C72" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
       <c r="D72" t="s">
         <v>299</v>
       </c>
       <c r="E72" t="s">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="F72" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>629</v>
+      </c>
+      <c r="B73" t="s">
+        <v>630</v>
+      </c>
+      <c r="C73" t="s">
+        <v>631</v>
+      </c>
+      <c r="D73" t="s">
+        <v>318</v>
+      </c>
+      <c r="E73" t="s">
+        <v>632</v>
+      </c>
+      <c r="F73" t="s">
+        <v>633</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>635</v>
+      </c>
+      <c r="B74" t="s">
+        <v>636</v>
+      </c>
+      <c r="C74" t="s">
+        <v>374</v>
+      </c>
+      <c r="D74" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" t="s">
+        <v>637</v>
+      </c>
+      <c r="F74" t="s">
+        <v>638</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>640</v>
+      </c>
+      <c r="B75" t="s">
+        <v>641</v>
+      </c>
+      <c r="C75" t="s">
+        <v>642</v>
+      </c>
+      <c r="D75" t="s">
+        <v>299</v>
+      </c>
+      <c r="E75" t="s">
+        <v>643</v>
+      </c>
+      <c r="F75" t="s">
+        <v>644</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>646</v>
+      </c>
+      <c r="B76" t="s">
+        <v>647</v>
+      </c>
+      <c r="C76" t="s">
+        <v>305</v>
+      </c>
+      <c r="D76" t="s">
+        <v>299</v>
+      </c>
+      <c r="E76" t="s">
+        <v>648</v>
+      </c>
+      <c r="F76" t="s">
+        <v>649</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
         <v>651</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B77" t="s">
         <v>652</v>
       </c>
-      <c r="C73" t="s">
-        <v>311</v>
-      </c>
-      <c r="D73" t="s">
-        <v>299</v>
-      </c>
-      <c r="E73" t="s">
+      <c r="C77" t="s">
         <v>653</v>
       </c>
-      <c r="F73" t="s">
-        <v>399</v>
-      </c>
-      <c r="H73" s="2" t="s">
+      <c r="D77" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" t="s">
         <v>654</v>
+      </c>
+      <c r="F77" t="s">
+        <v>655</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>657</v>
+      </c>
+      <c r="B78" t="s">
+        <v>447</v>
+      </c>
+      <c r="C78" t="s">
+        <v>317</v>
+      </c>
+      <c r="D78" t="s">
+        <v>299</v>
+      </c>
+      <c r="E78" t="s">
+        <v>543</v>
+      </c>
+      <c r="F78" t="s">
+        <v>448</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>659</v>
+      </c>
+      <c r="B79" t="s">
+        <v>402</v>
+      </c>
+      <c r="C79" t="s">
+        <v>229</v>
+      </c>
+      <c r="D79" t="s">
+        <v>299</v>
+      </c>
+      <c r="E79" t="s">
+        <v>660</v>
+      </c>
+      <c r="F79" t="s">
+        <v>320</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>662</v>
+      </c>
+      <c r="B80" t="s">
+        <v>663</v>
+      </c>
+      <c r="C80" t="s">
+        <v>664</v>
+      </c>
+      <c r="D80" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" t="s">
+        <v>665</v>
+      </c>
+      <c r="F80" t="s">
+        <v>666</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>668</v>
+      </c>
+      <c r="B81" t="s">
+        <v>669</v>
+      </c>
+      <c r="C81" t="s">
+        <v>670</v>
+      </c>
+      <c r="D81" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" t="s">
+        <v>671</v>
+      </c>
+      <c r="F81" t="s">
+        <v>672</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>674</v>
+      </c>
+      <c r="B82" t="s">
+        <v>675</v>
+      </c>
+      <c r="C82" t="s">
+        <v>676</v>
+      </c>
+      <c r="D82" t="s">
+        <v>299</v>
+      </c>
+      <c r="E82" t="s">
+        <v>677</v>
+      </c>
+      <c r="F82" t="s">
+        <v>613</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>679</v>
+      </c>
+      <c r="B83" t="s">
+        <v>680</v>
+      </c>
+      <c r="C83" t="s">
+        <v>324</v>
+      </c>
+      <c r="D83" t="s">
+        <v>299</v>
+      </c>
+      <c r="E83" t="s">
+        <v>681</v>
+      </c>
+      <c r="F83" t="s">
+        <v>682</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>684</v>
+      </c>
+      <c r="B84" t="s">
+        <v>685</v>
+      </c>
+      <c r="C84" t="s">
+        <v>653</v>
+      </c>
+      <c r="D84" t="s">
+        <v>299</v>
+      </c>
+      <c r="E84" t="s">
+        <v>686</v>
+      </c>
+      <c r="F84" t="s">
+        <v>415</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>688</v>
+      </c>
+      <c r="B85" t="s">
+        <v>689</v>
+      </c>
+      <c r="C85" t="s">
+        <v>305</v>
+      </c>
+      <c r="D85" t="s">
+        <v>299</v>
+      </c>
+      <c r="E85" t="s">
+        <v>690</v>
+      </c>
+      <c r="F85" t="s">
+        <v>301</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>692</v>
+      </c>
+      <c r="B86" t="s">
+        <v>693</v>
+      </c>
+      <c r="C86" t="s">
+        <v>305</v>
+      </c>
+      <c r="D86" t="s">
+        <v>299</v>
+      </c>
+      <c r="E86" t="s">
+        <v>694</v>
+      </c>
+      <c r="F86" t="s">
+        <v>695</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>697</v>
+      </c>
+      <c r="B87" t="s">
+        <v>698</v>
+      </c>
+      <c r="C87" t="s">
+        <v>324</v>
+      </c>
+      <c r="D87" t="s">
+        <v>299</v>
+      </c>
+      <c r="E87" t="s">
+        <v>699</v>
+      </c>
+      <c r="F87" t="s">
+        <v>700</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>702</v>
+      </c>
+      <c r="B88" t="s">
+        <v>335</v>
+      </c>
+      <c r="C88" t="s">
+        <v>305</v>
+      </c>
+      <c r="D88" t="s">
+        <v>299</v>
+      </c>
+      <c r="E88" t="s">
+        <v>703</v>
+      </c>
+      <c r="F88" t="s">
+        <v>420</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>705</v>
+      </c>
+      <c r="B89" t="s">
+        <v>706</v>
+      </c>
+      <c r="C89" t="s">
+        <v>305</v>
+      </c>
+      <c r="D89" t="s">
+        <v>299</v>
+      </c>
+      <c r="E89" t="s">
+        <v>707</v>
+      </c>
+      <c r="F89" t="s">
+        <v>708</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>710</v>
+      </c>
+      <c r="B90" t="s">
+        <v>541</v>
+      </c>
+      <c r="C90" t="s">
+        <v>542</v>
+      </c>
+      <c r="D90" t="s">
+        <v>299</v>
+      </c>
+      <c r="E90" t="s">
+        <v>711</v>
+      </c>
+      <c r="F90" t="s">
+        <v>544</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>713</v>
+      </c>
+      <c r="B91" t="s">
+        <v>714</v>
+      </c>
+      <c r="C91" t="s">
+        <v>715</v>
+      </c>
+      <c r="D91" t="s">
+        <v>299</v>
+      </c>
+      <c r="E91" t="s">
+        <v>716</v>
+      </c>
+      <c r="F91" t="s">
+        <v>717</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>719</v>
+      </c>
+      <c r="B92" t="s">
+        <v>693</v>
+      </c>
+      <c r="C92" t="s">
+        <v>305</v>
+      </c>
+      <c r="D92" t="s">
+        <v>299</v>
+      </c>
+      <c r="E92" t="s">
+        <v>720</v>
+      </c>
+      <c r="F92" t="s">
+        <v>695</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>722</v>
+      </c>
+      <c r="B93" t="s">
+        <v>447</v>
+      </c>
+      <c r="C93" t="s">
+        <v>317</v>
+      </c>
+      <c r="D93" t="s">
+        <v>299</v>
+      </c>
+      <c r="E93" t="s">
+        <v>723</v>
+      </c>
+      <c r="F93" t="s">
+        <v>448</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>725</v>
+      </c>
+      <c r="B94" t="s">
+        <v>726</v>
+      </c>
+      <c r="C94" t="s">
+        <v>727</v>
+      </c>
+      <c r="D94" t="s">
+        <v>299</v>
+      </c>
+      <c r="E94" t="s">
+        <v>728</v>
+      </c>
+      <c r="F94" t="s">
+        <v>729</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>731</v>
+      </c>
+      <c r="B95" t="s">
+        <v>732</v>
+      </c>
+      <c r="C95" t="s">
+        <v>733</v>
+      </c>
+      <c r="D95" t="s">
+        <v>375</v>
+      </c>
+      <c r="E95" t="s">
+        <v>734</v>
+      </c>
+      <c r="F95" t="s">
+        <v>735</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>237</v>
+      </c>
+      <c r="B96" t="s">
+        <v>737</v>
+      </c>
+      <c r="C96" t="s">
+        <v>324</v>
+      </c>
+      <c r="D96" t="s">
+        <v>299</v>
+      </c>
+      <c r="E96" t="s">
+        <v>738</v>
+      </c>
+      <c r="F96" t="s">
+        <v>739</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>237</v>
+      </c>
+      <c r="B97" t="s">
+        <v>741</v>
+      </c>
+      <c r="C97" t="s">
+        <v>317</v>
+      </c>
+      <c r="D97" t="s">
+        <v>299</v>
+      </c>
+      <c r="E97" t="s">
+        <v>742</v>
+      </c>
+      <c r="F97" t="s">
+        <v>743</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>745</v>
+      </c>
+      <c r="B98" t="s">
+        <v>625</v>
+      </c>
+      <c r="C98" t="s">
+        <v>317</v>
+      </c>
+      <c r="D98" t="s">
+        <v>299</v>
+      </c>
+      <c r="E98" t="s">
+        <v>626</v>
+      </c>
+      <c r="F98" t="s">
+        <v>627</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>747</v>
+      </c>
+      <c r="B99" t="s">
+        <v>748</v>
+      </c>
+      <c r="C99" t="s">
+        <v>631</v>
+      </c>
+      <c r="D99" t="s">
+        <v>299</v>
+      </c>
+      <c r="E99" t="s">
+        <v>749</v>
+      </c>
+      <c r="F99" t="s">
+        <v>750</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>752</v>
+      </c>
+      <c r="B100" t="s">
+        <v>753</v>
+      </c>
+      <c r="C100" t="s">
+        <v>298</v>
+      </c>
+      <c r="D100" t="s">
+        <v>299</v>
+      </c>
+      <c r="E100" t="s">
+        <v>754</v>
+      </c>
+      <c r="F100" t="s">
+        <v>755</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>757</v>
+      </c>
+      <c r="B101" t="s">
+        <v>447</v>
+      </c>
+      <c r="C101" t="s">
+        <v>317</v>
+      </c>
+      <c r="D101" t="s">
+        <v>299</v>
+      </c>
+      <c r="E101" t="s">
+        <v>758</v>
+      </c>
+      <c r="F101" t="s">
+        <v>448</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>760</v>
+      </c>
+      <c r="B102" t="s">
+        <v>761</v>
+      </c>
+      <c r="C102" t="s">
+        <v>503</v>
+      </c>
+      <c r="D102" t="s">
+        <v>299</v>
+      </c>
+      <c r="E102" t="s">
+        <v>762</v>
+      </c>
+      <c r="F102" t="s">
+        <v>763</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>765</v>
+      </c>
+      <c r="B103" t="s">
+        <v>766</v>
+      </c>
+      <c r="C103" t="s">
+        <v>324</v>
+      </c>
+      <c r="D103" t="s">
+        <v>299</v>
+      </c>
+      <c r="E103" t="s">
+        <v>767</v>
+      </c>
+      <c r="F103" t="s">
+        <v>420</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>768</v>
       </c>
     </row>
   </sheetData>
@@ -5600,6 +6632,36 @@
     <hyperlink ref="H71" r:id="rId70"/>
     <hyperlink ref="H72" r:id="rId71"/>
     <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
